--- a/src/main/resources/client-labels/ami-etiquetas-template.xlsx
+++ b/src/main/resources/client-labels/ami-etiquetas-template.xlsx
@@ -20,22 +20,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="42">
   <si>
-    <t>SCHENKER</t>
-  </si>
-  <si>
     <t>DHL GLOBAL FORWARDING CO.LTD</t>
-  </si>
-  <si>
-    <t>ID LOGISTICS</t>
   </si>
   <si>
     <t>C/O AMI</t>
   </si>
   <si>
     <t>N°305 HUTING RD</t>
-  </si>
-  <si>
-    <t>XXXXX</t>
   </si>
   <si>
     <t>SONG JIANG DISTRICT</t>
@@ -59,16 +50,7 @@
     </r>
   </si>
   <si>
-    <t>SUPPLIER CODE</t>
-  </si>
-  <si>
     <t>CHINA</t>
-  </si>
-  <si>
-    <t>JAPAN</t>
-  </si>
-  <si>
-    <t>A.PARIS</t>
   </si>
   <si>
     <r>
@@ -92,49 +74,7 @@
     </r>
   </si>
   <si>
-    <t>21 avenue Saint Mathurins</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="14.0"/>
-        <u/>
-      </rPr>
-      <t>SUPPLIER CODE</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="14.0"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="18.0"/>
-      </rPr>
-      <t>PUN</t>
-    </r>
-  </si>
-  <si>
-    <t>PUN</t>
-  </si>
-  <si>
     <t>ORDER NUMBER</t>
-  </si>
-  <si>
-    <t>60000 ALLONNE</t>
-  </si>
-  <si>
-    <t>France</t>
   </si>
   <si>
     <t>REFERENCE</t>
@@ -146,16 +86,7 @@
     <t>ULL163.AL0052</t>
   </si>
   <si>
-    <t>ULL745.AL0103</t>
-  </si>
-  <si>
     <t>COLOR CODE</t>
-  </si>
-  <si>
-    <t>001 BLACK</t>
-  </si>
-  <si>
-    <t>UBL029.AL0216</t>
   </si>
   <si>
     <t>SIZE</t>
@@ -167,34 +98,16 @@
     <t>QUANTITY</t>
   </si>
   <si>
-    <t>85-95-105</t>
-  </si>
-  <si>
     <t>GROSS WEIGHT</t>
-  </si>
-  <si>
-    <t>4,98 kgs</t>
   </si>
   <si>
     <t>5,28 KGS</t>
   </si>
   <si>
-    <t>4-85, 33-95, 4-105</t>
-  </si>
-  <si>
     <t>PARCEL N° / TOTAL NUMBER OF PARCELS</t>
   </si>
   <si>
-    <t>8 / 8</t>
-  </si>
-  <si>
     <t>15 / 15</t>
-  </si>
-  <si>
-    <t>9,93 KG</t>
-  </si>
-  <si>
-    <t>14 / 84</t>
   </si>
   <si>
     <r>
@@ -236,6 +149,18 @@
     </r>
   </si>
   <si>
+    <t>SCHENKER</t>
+  </si>
+  <si>
+    <t>XXXXX</t>
+  </si>
+  <si>
+    <t>ID LOGISTICS</t>
+  </si>
+  <si>
+    <t>JAPAN</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Calibri"/>
@@ -265,6 +190,81 @@
       <t>PUN</t>
     </r>
   </si>
+  <si>
+    <t>SUPPLIER CODE</t>
+  </si>
+  <si>
+    <t>A.PARIS</t>
+  </si>
+  <si>
+    <t>21 avenue Saint Mathurins</t>
+  </si>
+  <si>
+    <t>PUN</t>
+  </si>
+  <si>
+    <t>ULL745.AL0103</t>
+  </si>
+  <si>
+    <t>60000 ALLONNE</t>
+  </si>
+  <si>
+    <t>001 BLACK</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>4,98 kgs</t>
+  </si>
+  <si>
+    <t>8 / 8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="14.0"/>
+        <u/>
+      </rPr>
+      <t>SUPPLIER CODE</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="14.0"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="18.0"/>
+      </rPr>
+      <t>PUN</t>
+    </r>
+  </si>
+  <si>
+    <t>UBL029.AL0216</t>
+  </si>
+  <si>
+    <t>85-95-105</t>
+  </si>
+  <si>
+    <t>4-85, 33-95, 4-105</t>
+  </si>
+  <si>
+    <t>9,93 KG</t>
+  </si>
+  <si>
+    <t>14 / 84</t>
+  </si>
 </sst>
 </file>
 
@@ -281,17 +281,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22.0"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="16.0"/>
       <color theme="1"/>
@@ -299,25 +288,7 @@
     </font>
     <font/>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -329,7 +300,7 @@
     </font>
     <font>
       <b/>
-      <sz val="36.0"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -351,11 +322,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="20.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="28.0"/>
       <color theme="1"/>
@@ -368,9 +334,38 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
-      <sz val="28.0"/>
+      <sz val="22.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22.0"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -381,24 +376,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="19.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="19.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -407,6 +385,28 @@
       <i/>
       <sz val="12.0"/>
       <color theme="5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="20.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="19.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -449,27 +449,6 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -497,36 +476,6 @@
       </right>
       <top/>
       <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
     </border>
     <border>
       <left style="medium">
@@ -576,16 +525,12 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
     </border>
     <border>
@@ -595,9 +540,8 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="medium">
@@ -630,18 +574,9 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -656,7 +591,7 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -681,10 +616,75 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -715,199 +715,199 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="14" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="12" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="16" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="17" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="18" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="17" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf quotePrefix="1" borderId="19" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="18" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="10" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="20" fillId="0" fontId="20" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="22" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="23" fillId="3" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf quotePrefix="1" borderId="20" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="10" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="15" fillId="0" fontId="22" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="11" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="0" fontId="18" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="2" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="17" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf quotePrefix="1" borderId="15" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf quotePrefix="1" borderId="9" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="19" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="2" fontId="20" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="2" fontId="22" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="17" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="20" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="4" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="3" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="3" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="3" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="26" fillId="3" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -930,7 +930,7 @@
     <xdr:ext cx="1047750" cy="666750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.gif"/>
+        <xdr:cNvPr id="0" name="image3.gif"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -958,7 +958,7 @@
     <xdr:ext cx="1047750" cy="666750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.gif"/>
+        <xdr:cNvPr id="0" name="image3.gif"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1108,7 +1108,7 @@
     <xdr:ext cx="1209675" cy="762000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.gif"/>
+        <xdr:cNvPr id="0" name="image2.gif"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1136,7 +1136,7 @@
     <xdr:ext cx="1209675" cy="762000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.gif"/>
+        <xdr:cNvPr id="0" name="image2.gif"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1366,220 +1366,220 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" ht="30.0" customHeight="1">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="7" t="s">
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" ht="33.75" customHeight="1">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" ht="23.25" customHeight="1">
+      <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" ht="30.0" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" ht="27.0" customHeight="1">
+      <c r="B9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" ht="41.25" customHeight="1">
-      <c r="B7" s="12" t="s">
+      <c r="C9" s="10"/>
+    </row>
+    <row r="10" ht="27.0" customHeight="1">
+      <c r="B10" s="11"/>
+      <c r="C10" s="12">
+        <v>7703.0</v>
+      </c>
+    </row>
+    <row r="11" ht="29.25" customHeight="1">
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="13"/>
+    </row>
+    <row r="12" ht="36.75" customHeight="1">
+      <c r="B12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="14"/>
-    </row>
-    <row r="8" ht="23.25" customHeight="1">
-      <c r="B8" s="17" t="s">
+      <c r="C12" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" ht="36.75" customHeight="1">
+      <c r="B13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="16">
+        <v>221.0</v>
+      </c>
+    </row>
+    <row r="14" ht="31.5" customHeight="1">
+      <c r="B14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="19"/>
-    </row>
-    <row r="9" ht="27.0" customHeight="1">
-      <c r="B9" s="23" t="s">
+      <c r="C14" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="28.5" customHeight="1">
+      <c r="B15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="20">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="16" ht="26.25" customHeight="1">
+      <c r="B16" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="25"/>
-    </row>
-    <row r="10" ht="27.0" customHeight="1">
-      <c r="B10" s="28"/>
-      <c r="C10" s="29">
+      <c r="D16" s="23"/>
+    </row>
+    <row r="17" ht="57.0" customHeight="1">
+      <c r="B17" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" ht="21.0" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="B20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" ht="30.0" customHeight="1">
+      <c r="B23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" ht="33.75" customHeight="1">
+      <c r="B24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" ht="23.25" customHeight="1">
+      <c r="B25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" ht="27.0" customHeight="1">
+      <c r="B26" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" ht="27.0" customHeight="1">
+      <c r="B27" s="11"/>
+      <c r="C27" s="12">
         <v>7703.0</v>
       </c>
     </row>
-    <row r="11" ht="36.75" customHeight="1">
-      <c r="B11" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="33"/>
-    </row>
-    <row r="12" ht="36.75" customHeight="1">
-      <c r="B12" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" ht="36.75" customHeight="1">
-      <c r="B13" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="43">
+    <row r="28" ht="29.25" customHeight="1">
+      <c r="B28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="13"/>
+    </row>
+    <row r="29" ht="36.75" customHeight="1">
+      <c r="B29" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" ht="36.75" customHeight="1">
+      <c r="B30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="16">
         <v>221.0</v>
       </c>
     </row>
-    <row r="14" ht="36.75" customHeight="1">
-      <c r="B14" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" ht="28.5" customHeight="1">
-      <c r="B15" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="49">
+    <row r="31" ht="31.5" customHeight="1">
+      <c r="B31" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" ht="28.5" customHeight="1">
+      <c r="B32" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="20">
         <v>5.0</v>
       </c>
     </row>
-    <row r="16" ht="26.25" customHeight="1">
-      <c r="B16" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="52"/>
-    </row>
-    <row r="17" ht="57.0" customHeight="1">
-      <c r="B17" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" ht="21.0" customHeight="1">
-      <c r="B19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="B20" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="B22" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" ht="30.0" customHeight="1">
-      <c r="B23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" ht="41.25" customHeight="1">
-      <c r="B24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="14"/>
-    </row>
-    <row r="25" ht="23.25" customHeight="1">
-      <c r="B25" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="19"/>
-    </row>
-    <row r="26" ht="27.0" customHeight="1">
-      <c r="B26" s="23" t="s">
+    <row r="33" ht="26.25" customHeight="1">
+      <c r="B33" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="25"/>
-    </row>
-    <row r="27" ht="27.0" customHeight="1">
-      <c r="B27" s="28"/>
-      <c r="C27" s="29">
-        <v>7703.0</v>
-      </c>
-    </row>
-    <row r="28" ht="36.75" customHeight="1">
-      <c r="B28" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="33"/>
-    </row>
-    <row r="29" ht="36.75" customHeight="1">
-      <c r="B29" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" ht="36.75" customHeight="1">
-      <c r="B30" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="43">
-        <v>221.0</v>
-      </c>
-    </row>
-    <row r="31" ht="36.75" customHeight="1">
-      <c r="B31" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" ht="28.5" customHeight="1">
-      <c r="B32" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="49">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="33" ht="26.25" customHeight="1">
-      <c r="B33" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="53" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="34" ht="57.0" customHeight="1">
-      <c r="B34" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="58" t="s">
-        <v>36</v>
+      <c r="B34" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2583,206 +2583,206 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1"/>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="8"/>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" ht="67.5" customHeight="1">
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="15"/>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" ht="60.0" customHeight="1">
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="29"/>
     </row>
     <row r="7" ht="41.25" customHeight="1">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="33"/>
+    </row>
+    <row r="8" ht="27.0" customHeight="1">
+      <c r="B8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="35"/>
+    </row>
+    <row r="9" ht="27.0" customHeight="1">
+      <c r="B9" s="11"/>
+      <c r="C9" s="39">
+        <v>7697.0</v>
+      </c>
+    </row>
+    <row r="10" ht="23.25" customHeight="1">
+      <c r="B10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="13"/>
+    </row>
+    <row r="11" ht="36.75" customHeight="1">
+      <c r="B11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" ht="36.75" customHeight="1">
+      <c r="B12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" ht="36.75" customHeight="1">
+      <c r="B13" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="36.75" customHeight="1">
+      <c r="B14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="22"/>
-    </row>
-    <row r="8" ht="27.0" customHeight="1">
-      <c r="B8" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="26"/>
-    </row>
-    <row r="9" ht="27.0" customHeight="1">
-      <c r="B9" s="28"/>
-      <c r="C9" s="31">
+      <c r="C14" s="20">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15" ht="28.5" customHeight="1">
+      <c r="B15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="23"/>
+    </row>
+    <row r="16" ht="51.75" customHeight="1">
+      <c r="B16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="30.0" customHeight="1">
+      <c r="B17" s="47"/>
+    </row>
+    <row r="18" ht="21.0" customHeight="1">
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="B20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" ht="60.0" customHeight="1">
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="29"/>
+    </row>
+    <row r="23" ht="41.25" customHeight="1">
+      <c r="B23" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="33"/>
+    </row>
+    <row r="24" ht="27.0" customHeight="1">
+      <c r="B24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="35"/>
+    </row>
+    <row r="25" ht="27.0" customHeight="1">
+      <c r="B25" s="11"/>
+      <c r="C25" s="39">
         <v>7697.0</v>
       </c>
     </row>
-    <row r="10" ht="23.25" customHeight="1">
-      <c r="B10" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="33"/>
-    </row>
-    <row r="11" ht="36.75" customHeight="1">
-      <c r="B11" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="36.75" customHeight="1">
-      <c r="B12" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" ht="36.75" customHeight="1">
-      <c r="B13" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" ht="36.75" customHeight="1">
-      <c r="B14" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="49">
+    <row r="26" ht="23.25" customHeight="1">
+      <c r="B26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="13"/>
+    </row>
+    <row r="27" ht="36.75" customHeight="1">
+      <c r="B27" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="36.75" customHeight="1">
+      <c r="B28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" ht="36.75" customHeight="1">
+      <c r="B29" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="36.75" customHeight="1">
+      <c r="B30" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="20">
         <v>1.0</v>
       </c>
     </row>
-    <row r="15" ht="28.5" customHeight="1">
-      <c r="B15" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="52"/>
-    </row>
-    <row r="16" ht="65.25" customHeight="1">
-      <c r="B16" s="54" t="s">
+    <row r="31" ht="28.5" customHeight="1">
+      <c r="B31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" ht="30.0" customHeight="1">
-      <c r="B17" s="59"/>
-    </row>
-    <row r="18" ht="21.0" customHeight="1">
-      <c r="B18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="B20" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" ht="67.5" customHeight="1">
-      <c r="B22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="15"/>
-    </row>
-    <row r="23" ht="41.25" customHeight="1">
-      <c r="B23" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="22"/>
-    </row>
-    <row r="24" ht="27.0" customHeight="1">
-      <c r="B24" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="26"/>
-    </row>
-    <row r="25" ht="27.0" customHeight="1">
-      <c r="B25" s="28"/>
-      <c r="C25" s="31">
-        <v>7697.0</v>
-      </c>
-    </row>
-    <row r="26" ht="23.25" customHeight="1">
-      <c r="B26" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="33"/>
-    </row>
-    <row r="27" ht="36.75" customHeight="1">
-      <c r="B27" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" ht="36.75" customHeight="1">
-      <c r="B28" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" ht="36.75" customHeight="1">
-      <c r="B29" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" ht="36.75" customHeight="1">
-      <c r="B30" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="49">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="31" ht="28.5" customHeight="1">
-      <c r="B31" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" ht="65.25" customHeight="1">
-      <c r="B32" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="56" t="s">
+    </row>
+    <row r="32" ht="51.75" customHeight="1">
+      <c r="B32" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="46" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3787,3153 +3787,3153 @@
   </cols>
   <sheetData>
     <row r="1" ht="9.0" customHeight="1">
-      <c r="B1" s="1"/>
+      <c r="B1" s="26"/>
     </row>
     <row r="2" ht="40.5" customHeight="1">
-      <c r="B2" s="2"/>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="30"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="30"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="30"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="B5" s="38"/>
+      <c r="C5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="30"/>
+    </row>
+    <row r="6" ht="24.75" customHeight="1">
+      <c r="B6" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="30"/>
+    </row>
+    <row r="7" ht="24.0" customHeight="1">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="30"/>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="B8" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="48"/>
+      <c r="D8" s="30"/>
+      <c r="F8" s="49"/>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="B9" s="32"/>
+      <c r="C9" s="50">
+        <v>7672.0</v>
+      </c>
+      <c r="D9" s="30"/>
+    </row>
+    <row r="10" ht="24.0" customHeight="1">
+      <c r="B10" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C10" s="52"/>
+      <c r="D10" s="30"/>
+    </row>
+    <row r="11" ht="36.0" customHeight="1">
+      <c r="B11" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="30"/>
+    </row>
+    <row r="12" ht="34.5" customHeight="1">
+      <c r="B12" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="16"/>
-      <c r="C5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" ht="24.75" customHeight="1">
-      <c r="B6" s="21" t="s">
+      <c r="C12" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="30"/>
+    </row>
+    <row r="13" ht="34.5" customHeight="1">
+      <c r="B13" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="30"/>
+    </row>
+    <row r="14" ht="34.5" customHeight="1">
+      <c r="B14" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="30"/>
+    </row>
+    <row r="15" ht="23.25" customHeight="1">
+      <c r="B15" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" ht="24.0" customHeight="1">
-      <c r="B7" s="24"/>
-      <c r="C7" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="B8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="6"/>
-      <c r="F8" s="32"/>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="B9" s="9"/>
-      <c r="C9" s="34">
-        <v>7672.0</v>
-      </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" ht="24.0" customHeight="1">
-      <c r="B10" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" ht="36.0" customHeight="1">
-      <c r="B11" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" ht="34.5" customHeight="1">
-      <c r="B12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" ht="34.5" customHeight="1">
-      <c r="B13" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" ht="34.5" customHeight="1">
-      <c r="B14" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" ht="23.25" customHeight="1">
-      <c r="B15" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="6"/>
+      <c r="C15" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" ht="57.0" customHeight="1">
       <c r="B16" s="60" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="B17" s="1"/>
+      <c r="B17" s="26"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="B18" s="2"/>
-      <c r="C18" s="4" t="s">
-        <v>2</v>
+      <c r="B18" s="27"/>
+      <c r="C18" s="28" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="B19" s="62"/>
-      <c r="C19" s="10"/>
+      <c r="C19" s="34"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="B20" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="B21" s="64"/>
-      <c r="C21" s="18" t="s">
-        <v>13</v>
+      <c r="C21" s="40" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="B22" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="B23" s="66"/>
-      <c r="C23" s="27" t="s">
-        <v>18</v>
+      <c r="C23" s="45" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="B24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="6"/>
-      <c r="F24" s="32"/>
+      <c r="B24" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="30"/>
+      <c r="F24" s="49"/>
       <c r="I24" s="67"/>
     </row>
     <row r="25" ht="40.5" customHeight="1">
-      <c r="B25" s="9"/>
-      <c r="C25" s="34">
+      <c r="B25" s="32"/>
+      <c r="C25" s="50">
         <v>7672.0</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="30"/>
       <c r="I25" s="68"/>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="B26" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="6"/>
+      <c r="B26" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="30"/>
       <c r="I26" s="69"/>
     </row>
     <row r="27" ht="36.0" customHeight="1">
-      <c r="B27" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="6"/>
+      <c r="B27" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="30"/>
       <c r="I27" s="70"/>
     </row>
     <row r="28" ht="34.5" customHeight="1">
-      <c r="B28" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="6"/>
+      <c r="B28" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="30"/>
       <c r="I28" s="71"/>
     </row>
     <row r="29" ht="34.5" customHeight="1">
-      <c r="B29" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="6"/>
+      <c r="B29" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="30"/>
     </row>
     <row r="30" ht="34.5" customHeight="1">
-      <c r="B30" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="6"/>
+      <c r="B30" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="30"/>
     </row>
     <row r="31" ht="23.25" customHeight="1">
-      <c r="B31" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="6"/>
+      <c r="B31" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="30"/>
     </row>
     <row r="32" ht="57.0" customHeight="1">
       <c r="B32" s="60" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="D32" s="30"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="B33" s="1"/>
+      <c r="B33" s="26"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="B34" s="1"/>
+      <c r="B34" s="26"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="B35" s="1"/>
+      <c r="B35" s="26"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="B36" s="1"/>
+      <c r="B36" s="26"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="B37" s="1"/>
+      <c r="B37" s="26"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="B38" s="1"/>
+      <c r="B38" s="26"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="B39" s="1"/>
+      <c r="B39" s="26"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="B40" s="1"/>
+      <c r="B40" s="26"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="B41" s="1"/>
+      <c r="B41" s="26"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="B42" s="1"/>
+      <c r="B42" s="26"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="B43" s="1"/>
+      <c r="B43" s="26"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="B44" s="1"/>
+      <c r="B44" s="26"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="B45" s="1"/>
+      <c r="B45" s="26"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="B46" s="1"/>
+      <c r="B46" s="26"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="B47" s="1"/>
+      <c r="B47" s="26"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="B48" s="1"/>
+      <c r="B48" s="26"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="B49" s="1"/>
+      <c r="B49" s="26"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="B50" s="1"/>
+      <c r="B50" s="26"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="B51" s="1"/>
+      <c r="B51" s="26"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="B52" s="1"/>
+      <c r="B52" s="26"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="B53" s="1"/>
+      <c r="B53" s="26"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="B54" s="1"/>
+      <c r="B54" s="26"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="B55" s="1"/>
+      <c r="B55" s="26"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="B56" s="1"/>
+      <c r="B56" s="26"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="B57" s="1"/>
+      <c r="B57" s="26"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="B58" s="1"/>
+      <c r="B58" s="26"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="B59" s="1"/>
+      <c r="B59" s="26"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="B60" s="1"/>
+      <c r="B60" s="26"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="B61" s="1"/>
+      <c r="B61" s="26"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="B62" s="1"/>
+      <c r="B62" s="26"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="B63" s="1"/>
+      <c r="B63" s="26"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="B64" s="1"/>
+      <c r="B64" s="26"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="B65" s="1"/>
+      <c r="B65" s="26"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="B66" s="1"/>
+      <c r="B66" s="26"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="B67" s="1"/>
+      <c r="B67" s="26"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="B68" s="1"/>
+      <c r="B68" s="26"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="B69" s="1"/>
+      <c r="B69" s="26"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="B70" s="1"/>
+      <c r="B70" s="26"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="B71" s="1"/>
+      <c r="B71" s="26"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="B72" s="1"/>
+      <c r="B72" s="26"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="B73" s="1"/>
+      <c r="B73" s="26"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="B74" s="1"/>
+      <c r="B74" s="26"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="B75" s="1"/>
+      <c r="B75" s="26"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="B76" s="1"/>
+      <c r="B76" s="26"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="B77" s="1"/>
+      <c r="B77" s="26"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="B78" s="1"/>
+      <c r="B78" s="26"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="B79" s="1"/>
+      <c r="B79" s="26"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="B80" s="1"/>
+      <c r="B80" s="26"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
-      <c r="B81" s="1"/>
+      <c r="B81" s="26"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
-      <c r="B82" s="1"/>
+      <c r="B82" s="26"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
-      <c r="B83" s="1"/>
+      <c r="B83" s="26"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
-      <c r="B84" s="1"/>
+      <c r="B84" s="26"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
-      <c r="B85" s="1"/>
+      <c r="B85" s="26"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
-      <c r="B86" s="1"/>
+      <c r="B86" s="26"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
-      <c r="B87" s="1"/>
+      <c r="B87" s="26"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
-      <c r="B88" s="1"/>
+      <c r="B88" s="26"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
-      <c r="B89" s="1"/>
+      <c r="B89" s="26"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
-      <c r="B90" s="1"/>
+      <c r="B90" s="26"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
-      <c r="B91" s="1"/>
+      <c r="B91" s="26"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
-      <c r="B92" s="1"/>
+      <c r="B92" s="26"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
-      <c r="B93" s="1"/>
+      <c r="B93" s="26"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
-      <c r="B94" s="1"/>
+      <c r="B94" s="26"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
-      <c r="B95" s="1"/>
+      <c r="B95" s="26"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
-      <c r="B96" s="1"/>
+      <c r="B96" s="26"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
-      <c r="B97" s="1"/>
+      <c r="B97" s="26"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
-      <c r="B98" s="1"/>
+      <c r="B98" s="26"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
-      <c r="B99" s="1"/>
+      <c r="B99" s="26"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
-      <c r="B100" s="1"/>
+      <c r="B100" s="26"/>
     </row>
     <row r="101" ht="18.75" customHeight="1">
-      <c r="B101" s="1"/>
+      <c r="B101" s="26"/>
     </row>
     <row r="102" ht="18.75" customHeight="1">
-      <c r="B102" s="1"/>
+      <c r="B102" s="26"/>
     </row>
     <row r="103" ht="18.75" customHeight="1">
-      <c r="B103" s="1"/>
+      <c r="B103" s="26"/>
     </row>
     <row r="104" ht="18.75" customHeight="1">
-      <c r="B104" s="1"/>
+      <c r="B104" s="26"/>
     </row>
     <row r="105" ht="18.75" customHeight="1">
-      <c r="B105" s="1"/>
+      <c r="B105" s="26"/>
     </row>
     <row r="106" ht="18.75" customHeight="1">
-      <c r="B106" s="1"/>
+      <c r="B106" s="26"/>
     </row>
     <row r="107" ht="18.75" customHeight="1">
-      <c r="B107" s="1"/>
+      <c r="B107" s="26"/>
     </row>
     <row r="108" ht="18.75" customHeight="1">
-      <c r="B108" s="1"/>
+      <c r="B108" s="26"/>
     </row>
     <row r="109" ht="18.75" customHeight="1">
-      <c r="B109" s="1"/>
+      <c r="B109" s="26"/>
     </row>
     <row r="110" ht="18.75" customHeight="1">
-      <c r="B110" s="1"/>
+      <c r="B110" s="26"/>
     </row>
     <row r="111" ht="18.75" customHeight="1">
-      <c r="B111" s="1"/>
+      <c r="B111" s="26"/>
     </row>
     <row r="112" ht="18.75" customHeight="1">
-      <c r="B112" s="1"/>
+      <c r="B112" s="26"/>
     </row>
     <row r="113" ht="18.75" customHeight="1">
-      <c r="B113" s="1"/>
+      <c r="B113" s="26"/>
     </row>
     <row r="114" ht="18.75" customHeight="1">
-      <c r="B114" s="1"/>
+      <c r="B114" s="26"/>
     </row>
     <row r="115" ht="18.75" customHeight="1">
-      <c r="B115" s="1"/>
+      <c r="B115" s="26"/>
     </row>
     <row r="116" ht="18.75" customHeight="1">
-      <c r="B116" s="1"/>
+      <c r="B116" s="26"/>
     </row>
     <row r="117" ht="18.75" customHeight="1">
-      <c r="B117" s="1"/>
+      <c r="B117" s="26"/>
     </row>
     <row r="118" ht="18.75" customHeight="1">
-      <c r="B118" s="1"/>
+      <c r="B118" s="26"/>
     </row>
     <row r="119" ht="18.75" customHeight="1">
-      <c r="B119" s="1"/>
+      <c r="B119" s="26"/>
     </row>
     <row r="120" ht="18.75" customHeight="1">
-      <c r="B120" s="1"/>
+      <c r="B120" s="26"/>
     </row>
     <row r="121" ht="18.75" customHeight="1">
-      <c r="B121" s="1"/>
+      <c r="B121" s="26"/>
     </row>
     <row r="122" ht="18.75" customHeight="1">
-      <c r="B122" s="1"/>
+      <c r="B122" s="26"/>
     </row>
     <row r="123" ht="18.75" customHeight="1">
-      <c r="B123" s="1"/>
+      <c r="B123" s="26"/>
     </row>
     <row r="124" ht="18.75" customHeight="1">
-      <c r="B124" s="1"/>
+      <c r="B124" s="26"/>
     </row>
     <row r="125" ht="18.75" customHeight="1">
-      <c r="B125" s="1"/>
+      <c r="B125" s="26"/>
     </row>
     <row r="126" ht="18.75" customHeight="1">
-      <c r="B126" s="1"/>
+      <c r="B126" s="26"/>
     </row>
     <row r="127" ht="18.75" customHeight="1">
-      <c r="B127" s="1"/>
+      <c r="B127" s="26"/>
     </row>
     <row r="128" ht="18.75" customHeight="1">
-      <c r="B128" s="1"/>
+      <c r="B128" s="26"/>
     </row>
     <row r="129" ht="18.75" customHeight="1">
-      <c r="B129" s="1"/>
+      <c r="B129" s="26"/>
     </row>
     <row r="130" ht="18.75" customHeight="1">
-      <c r="B130" s="1"/>
+      <c r="B130" s="26"/>
     </row>
     <row r="131" ht="18.75" customHeight="1">
-      <c r="B131" s="1"/>
+      <c r="B131" s="26"/>
     </row>
     <row r="132" ht="18.75" customHeight="1">
-      <c r="B132" s="1"/>
+      <c r="B132" s="26"/>
     </row>
     <row r="133" ht="18.75" customHeight="1">
-      <c r="B133" s="1"/>
+      <c r="B133" s="26"/>
     </row>
     <row r="134" ht="18.75" customHeight="1">
-      <c r="B134" s="1"/>
+      <c r="B134" s="26"/>
     </row>
     <row r="135" ht="18.75" customHeight="1">
-      <c r="B135" s="1"/>
+      <c r="B135" s="26"/>
     </row>
     <row r="136" ht="18.75" customHeight="1">
-      <c r="B136" s="1"/>
+      <c r="B136" s="26"/>
     </row>
     <row r="137" ht="18.75" customHeight="1">
-      <c r="B137" s="1"/>
+      <c r="B137" s="26"/>
     </row>
     <row r="138" ht="18.75" customHeight="1">
-      <c r="B138" s="1"/>
+      <c r="B138" s="26"/>
     </row>
     <row r="139" ht="18.75" customHeight="1">
-      <c r="B139" s="1"/>
+      <c r="B139" s="26"/>
     </row>
     <row r="140" ht="18.75" customHeight="1">
-      <c r="B140" s="1"/>
+      <c r="B140" s="26"/>
     </row>
     <row r="141" ht="18.75" customHeight="1">
-      <c r="B141" s="1"/>
+      <c r="B141" s="26"/>
     </row>
     <row r="142" ht="18.75" customHeight="1">
-      <c r="B142" s="1"/>
+      <c r="B142" s="26"/>
     </row>
     <row r="143" ht="18.75" customHeight="1">
-      <c r="B143" s="1"/>
+      <c r="B143" s="26"/>
     </row>
     <row r="144" ht="18.75" customHeight="1">
-      <c r="B144" s="1"/>
+      <c r="B144" s="26"/>
     </row>
     <row r="145" ht="18.75" customHeight="1">
-      <c r="B145" s="1"/>
+      <c r="B145" s="26"/>
     </row>
     <row r="146" ht="18.75" customHeight="1">
-      <c r="B146" s="1"/>
+      <c r="B146" s="26"/>
     </row>
     <row r="147" ht="18.75" customHeight="1">
-      <c r="B147" s="1"/>
+      <c r="B147" s="26"/>
     </row>
     <row r="148" ht="18.75" customHeight="1">
-      <c r="B148" s="1"/>
+      <c r="B148" s="26"/>
     </row>
     <row r="149" ht="18.75" customHeight="1">
-      <c r="B149" s="1"/>
+      <c r="B149" s="26"/>
     </row>
     <row r="150" ht="18.75" customHeight="1">
-      <c r="B150" s="1"/>
+      <c r="B150" s="26"/>
     </row>
     <row r="151" ht="18.75" customHeight="1">
-      <c r="B151" s="1"/>
+      <c r="B151" s="26"/>
     </row>
     <row r="152" ht="18.75" customHeight="1">
-      <c r="B152" s="1"/>
+      <c r="B152" s="26"/>
     </row>
     <row r="153" ht="18.75" customHeight="1">
-      <c r="B153" s="1"/>
+      <c r="B153" s="26"/>
     </row>
     <row r="154" ht="18.75" customHeight="1">
-      <c r="B154" s="1"/>
+      <c r="B154" s="26"/>
     </row>
     <row r="155" ht="18.75" customHeight="1">
-      <c r="B155" s="1"/>
+      <c r="B155" s="26"/>
     </row>
     <row r="156" ht="18.75" customHeight="1">
-      <c r="B156" s="1"/>
+      <c r="B156" s="26"/>
     </row>
     <row r="157" ht="18.75" customHeight="1">
-      <c r="B157" s="1"/>
+      <c r="B157" s="26"/>
     </row>
     <row r="158" ht="18.75" customHeight="1">
-      <c r="B158" s="1"/>
+      <c r="B158" s="26"/>
     </row>
     <row r="159" ht="18.75" customHeight="1">
-      <c r="B159" s="1"/>
+      <c r="B159" s="26"/>
     </row>
     <row r="160" ht="18.75" customHeight="1">
-      <c r="B160" s="1"/>
+      <c r="B160" s="26"/>
     </row>
     <row r="161" ht="18.75" customHeight="1">
-      <c r="B161" s="1"/>
+      <c r="B161" s="26"/>
     </row>
     <row r="162" ht="18.75" customHeight="1">
-      <c r="B162" s="1"/>
+      <c r="B162" s="26"/>
     </row>
     <row r="163" ht="18.75" customHeight="1">
-      <c r="B163" s="1"/>
+      <c r="B163" s="26"/>
     </row>
     <row r="164" ht="18.75" customHeight="1">
-      <c r="B164" s="1"/>
+      <c r="B164" s="26"/>
     </row>
     <row r="165" ht="18.75" customHeight="1">
-      <c r="B165" s="1"/>
+      <c r="B165" s="26"/>
     </row>
     <row r="166" ht="18.75" customHeight="1">
-      <c r="B166" s="1"/>
+      <c r="B166" s="26"/>
     </row>
     <row r="167" ht="18.75" customHeight="1">
-      <c r="B167" s="1"/>
+      <c r="B167" s="26"/>
     </row>
     <row r="168" ht="18.75" customHeight="1">
-      <c r="B168" s="1"/>
+      <c r="B168" s="26"/>
     </row>
     <row r="169" ht="18.75" customHeight="1">
-      <c r="B169" s="1"/>
+      <c r="B169" s="26"/>
     </row>
     <row r="170" ht="18.75" customHeight="1">
-      <c r="B170" s="1"/>
+      <c r="B170" s="26"/>
     </row>
     <row r="171" ht="18.75" customHeight="1">
-      <c r="B171" s="1"/>
+      <c r="B171" s="26"/>
     </row>
     <row r="172" ht="18.75" customHeight="1">
-      <c r="B172" s="1"/>
+      <c r="B172" s="26"/>
     </row>
     <row r="173" ht="18.75" customHeight="1">
-      <c r="B173" s="1"/>
+      <c r="B173" s="26"/>
     </row>
     <row r="174" ht="18.75" customHeight="1">
-      <c r="B174" s="1"/>
+      <c r="B174" s="26"/>
     </row>
     <row r="175" ht="18.75" customHeight="1">
-      <c r="B175" s="1"/>
+      <c r="B175" s="26"/>
     </row>
     <row r="176" ht="18.75" customHeight="1">
-      <c r="B176" s="1"/>
+      <c r="B176" s="26"/>
     </row>
     <row r="177" ht="18.75" customHeight="1">
-      <c r="B177" s="1"/>
+      <c r="B177" s="26"/>
     </row>
     <row r="178" ht="18.75" customHeight="1">
-      <c r="B178" s="1"/>
+      <c r="B178" s="26"/>
     </row>
     <row r="179" ht="18.75" customHeight="1">
-      <c r="B179" s="1"/>
+      <c r="B179" s="26"/>
     </row>
     <row r="180" ht="18.75" customHeight="1">
-      <c r="B180" s="1"/>
+      <c r="B180" s="26"/>
     </row>
     <row r="181" ht="18.75" customHeight="1">
-      <c r="B181" s="1"/>
+      <c r="B181" s="26"/>
     </row>
     <row r="182" ht="18.75" customHeight="1">
-      <c r="B182" s="1"/>
+      <c r="B182" s="26"/>
     </row>
     <row r="183" ht="18.75" customHeight="1">
-      <c r="B183" s="1"/>
+      <c r="B183" s="26"/>
     </row>
     <row r="184" ht="18.75" customHeight="1">
-      <c r="B184" s="1"/>
+      <c r="B184" s="26"/>
     </row>
     <row r="185" ht="18.75" customHeight="1">
-      <c r="B185" s="1"/>
+      <c r="B185" s="26"/>
     </row>
     <row r="186" ht="18.75" customHeight="1">
-      <c r="B186" s="1"/>
+      <c r="B186" s="26"/>
     </row>
     <row r="187" ht="18.75" customHeight="1">
-      <c r="B187" s="1"/>
+      <c r="B187" s="26"/>
     </row>
     <row r="188" ht="18.75" customHeight="1">
-      <c r="B188" s="1"/>
+      <c r="B188" s="26"/>
     </row>
     <row r="189" ht="18.75" customHeight="1">
-      <c r="B189" s="1"/>
+      <c r="B189" s="26"/>
     </row>
     <row r="190" ht="18.75" customHeight="1">
-      <c r="B190" s="1"/>
+      <c r="B190" s="26"/>
     </row>
     <row r="191" ht="18.75" customHeight="1">
-      <c r="B191" s="1"/>
+      <c r="B191" s="26"/>
     </row>
     <row r="192" ht="18.75" customHeight="1">
-      <c r="B192" s="1"/>
+      <c r="B192" s="26"/>
     </row>
     <row r="193" ht="18.75" customHeight="1">
-      <c r="B193" s="1"/>
+      <c r="B193" s="26"/>
     </row>
     <row r="194" ht="18.75" customHeight="1">
-      <c r="B194" s="1"/>
+      <c r="B194" s="26"/>
     </row>
     <row r="195" ht="18.75" customHeight="1">
-      <c r="B195" s="1"/>
+      <c r="B195" s="26"/>
     </row>
     <row r="196" ht="18.75" customHeight="1">
-      <c r="B196" s="1"/>
+      <c r="B196" s="26"/>
     </row>
     <row r="197" ht="18.75" customHeight="1">
-      <c r="B197" s="1"/>
+      <c r="B197" s="26"/>
     </row>
     <row r="198" ht="18.75" customHeight="1">
-      <c r="B198" s="1"/>
+      <c r="B198" s="26"/>
     </row>
     <row r="199" ht="18.75" customHeight="1">
-      <c r="B199" s="1"/>
+      <c r="B199" s="26"/>
     </row>
     <row r="200" ht="18.75" customHeight="1">
-      <c r="B200" s="1"/>
+      <c r="B200" s="26"/>
     </row>
     <row r="201" ht="18.75" customHeight="1">
-      <c r="B201" s="1"/>
+      <c r="B201" s="26"/>
     </row>
     <row r="202" ht="18.75" customHeight="1">
-      <c r="B202" s="1"/>
+      <c r="B202" s="26"/>
     </row>
     <row r="203" ht="18.75" customHeight="1">
-      <c r="B203" s="1"/>
+      <c r="B203" s="26"/>
     </row>
     <row r="204" ht="18.75" customHeight="1">
-      <c r="B204" s="1"/>
+      <c r="B204" s="26"/>
     </row>
     <row r="205" ht="18.75" customHeight="1">
-      <c r="B205" s="1"/>
+      <c r="B205" s="26"/>
     </row>
     <row r="206" ht="18.75" customHeight="1">
-      <c r="B206" s="1"/>
+      <c r="B206" s="26"/>
     </row>
     <row r="207" ht="18.75" customHeight="1">
-      <c r="B207" s="1"/>
+      <c r="B207" s="26"/>
     </row>
     <row r="208" ht="18.75" customHeight="1">
-      <c r="B208" s="1"/>
+      <c r="B208" s="26"/>
     </row>
     <row r="209" ht="18.75" customHeight="1">
-      <c r="B209" s="1"/>
+      <c r="B209" s="26"/>
     </row>
     <row r="210" ht="18.75" customHeight="1">
-      <c r="B210" s="1"/>
+      <c r="B210" s="26"/>
     </row>
     <row r="211" ht="18.75" customHeight="1">
-      <c r="B211" s="1"/>
+      <c r="B211" s="26"/>
     </row>
     <row r="212" ht="18.75" customHeight="1">
-      <c r="B212" s="1"/>
+      <c r="B212" s="26"/>
     </row>
     <row r="213" ht="18.75" customHeight="1">
-      <c r="B213" s="1"/>
+      <c r="B213" s="26"/>
     </row>
     <row r="214" ht="18.75" customHeight="1">
-      <c r="B214" s="1"/>
+      <c r="B214" s="26"/>
     </row>
     <row r="215" ht="18.75" customHeight="1">
-      <c r="B215" s="1"/>
+      <c r="B215" s="26"/>
     </row>
     <row r="216" ht="18.75" customHeight="1">
-      <c r="B216" s="1"/>
+      <c r="B216" s="26"/>
     </row>
     <row r="217" ht="18.75" customHeight="1">
-      <c r="B217" s="1"/>
+      <c r="B217" s="26"/>
     </row>
     <row r="218" ht="18.75" customHeight="1">
-      <c r="B218" s="1"/>
+      <c r="B218" s="26"/>
     </row>
     <row r="219" ht="18.75" customHeight="1">
-      <c r="B219" s="1"/>
+      <c r="B219" s="26"/>
     </row>
     <row r="220" ht="18.75" customHeight="1">
-      <c r="B220" s="1"/>
+      <c r="B220" s="26"/>
     </row>
     <row r="221" ht="18.75" customHeight="1">
-      <c r="B221" s="1"/>
+      <c r="B221" s="26"/>
     </row>
     <row r="222" ht="18.75" customHeight="1">
-      <c r="B222" s="1"/>
+      <c r="B222" s="26"/>
     </row>
     <row r="223" ht="18.75" customHeight="1">
-      <c r="B223" s="1"/>
+      <c r="B223" s="26"/>
     </row>
     <row r="224" ht="18.75" customHeight="1">
-      <c r="B224" s="1"/>
+      <c r="B224" s="26"/>
     </row>
     <row r="225" ht="18.75" customHeight="1">
-      <c r="B225" s="1"/>
+      <c r="B225" s="26"/>
     </row>
     <row r="226" ht="18.75" customHeight="1">
-      <c r="B226" s="1"/>
+      <c r="B226" s="26"/>
     </row>
     <row r="227" ht="18.75" customHeight="1">
-      <c r="B227" s="1"/>
+      <c r="B227" s="26"/>
     </row>
     <row r="228" ht="18.75" customHeight="1">
-      <c r="B228" s="1"/>
+      <c r="B228" s="26"/>
     </row>
     <row r="229" ht="18.75" customHeight="1">
-      <c r="B229" s="1"/>
+      <c r="B229" s="26"/>
     </row>
     <row r="230" ht="18.75" customHeight="1">
-      <c r="B230" s="1"/>
+      <c r="B230" s="26"/>
     </row>
     <row r="231" ht="18.75" customHeight="1">
-      <c r="B231" s="1"/>
+      <c r="B231" s="26"/>
     </row>
     <row r="232" ht="18.75" customHeight="1">
-      <c r="B232" s="1"/>
+      <c r="B232" s="26"/>
     </row>
     <row r="233" ht="18.75" customHeight="1">
-      <c r="B233" s="1"/>
+      <c r="B233" s="26"/>
     </row>
     <row r="234" ht="18.75" customHeight="1">
-      <c r="B234" s="1"/>
+      <c r="B234" s="26"/>
     </row>
     <row r="235" ht="18.75" customHeight="1">
-      <c r="B235" s="1"/>
+      <c r="B235" s="26"/>
     </row>
     <row r="236" ht="18.75" customHeight="1">
-      <c r="B236" s="1"/>
+      <c r="B236" s="26"/>
     </row>
     <row r="237" ht="18.75" customHeight="1">
-      <c r="B237" s="1"/>
+      <c r="B237" s="26"/>
     </row>
     <row r="238" ht="18.75" customHeight="1">
-      <c r="B238" s="1"/>
+      <c r="B238" s="26"/>
     </row>
     <row r="239" ht="18.75" customHeight="1">
-      <c r="B239" s="1"/>
+      <c r="B239" s="26"/>
     </row>
     <row r="240" ht="18.75" customHeight="1">
-      <c r="B240" s="1"/>
+      <c r="B240" s="26"/>
     </row>
     <row r="241" ht="18.75" customHeight="1">
-      <c r="B241" s="1"/>
+      <c r="B241" s="26"/>
     </row>
     <row r="242" ht="18.75" customHeight="1">
-      <c r="B242" s="1"/>
+      <c r="B242" s="26"/>
     </row>
     <row r="243" ht="18.75" customHeight="1">
-      <c r="B243" s="1"/>
+      <c r="B243" s="26"/>
     </row>
     <row r="244" ht="18.75" customHeight="1">
-      <c r="B244" s="1"/>
+      <c r="B244" s="26"/>
     </row>
     <row r="245" ht="18.75" customHeight="1">
-      <c r="B245" s="1"/>
+      <c r="B245" s="26"/>
     </row>
     <row r="246" ht="18.75" customHeight="1">
-      <c r="B246" s="1"/>
+      <c r="B246" s="26"/>
     </row>
     <row r="247" ht="18.75" customHeight="1">
-      <c r="B247" s="1"/>
+      <c r="B247" s="26"/>
     </row>
     <row r="248" ht="18.75" customHeight="1">
-      <c r="B248" s="1"/>
+      <c r="B248" s="26"/>
     </row>
     <row r="249" ht="18.75" customHeight="1">
-      <c r="B249" s="1"/>
+      <c r="B249" s="26"/>
     </row>
     <row r="250" ht="18.75" customHeight="1">
-      <c r="B250" s="1"/>
+      <c r="B250" s="26"/>
     </row>
     <row r="251" ht="18.75" customHeight="1">
-      <c r="B251" s="1"/>
+      <c r="B251" s="26"/>
     </row>
     <row r="252" ht="18.75" customHeight="1">
-      <c r="B252" s="1"/>
+      <c r="B252" s="26"/>
     </row>
     <row r="253" ht="18.75" customHeight="1">
-      <c r="B253" s="1"/>
+      <c r="B253" s="26"/>
     </row>
     <row r="254" ht="18.75" customHeight="1">
-      <c r="B254" s="1"/>
+      <c r="B254" s="26"/>
     </row>
     <row r="255" ht="18.75" customHeight="1">
-      <c r="B255" s="1"/>
+      <c r="B255" s="26"/>
     </row>
     <row r="256" ht="18.75" customHeight="1">
-      <c r="B256" s="1"/>
+      <c r="B256" s="26"/>
     </row>
     <row r="257" ht="18.75" customHeight="1">
-      <c r="B257" s="1"/>
+      <c r="B257" s="26"/>
     </row>
     <row r="258" ht="18.75" customHeight="1">
-      <c r="B258" s="1"/>
+      <c r="B258" s="26"/>
     </row>
     <row r="259" ht="18.75" customHeight="1">
-      <c r="B259" s="1"/>
+      <c r="B259" s="26"/>
     </row>
     <row r="260" ht="18.75" customHeight="1">
-      <c r="B260" s="1"/>
+      <c r="B260" s="26"/>
     </row>
     <row r="261" ht="18.75" customHeight="1">
-      <c r="B261" s="1"/>
+      <c r="B261" s="26"/>
     </row>
     <row r="262" ht="18.75" customHeight="1">
-      <c r="B262" s="1"/>
+      <c r="B262" s="26"/>
     </row>
     <row r="263" ht="18.75" customHeight="1">
-      <c r="B263" s="1"/>
+      <c r="B263" s="26"/>
     </row>
     <row r="264" ht="18.75" customHeight="1">
-      <c r="B264" s="1"/>
+      <c r="B264" s="26"/>
     </row>
     <row r="265" ht="18.75" customHeight="1">
-      <c r="B265" s="1"/>
+      <c r="B265" s="26"/>
     </row>
     <row r="266" ht="18.75" customHeight="1">
-      <c r="B266" s="1"/>
+      <c r="B266" s="26"/>
     </row>
     <row r="267" ht="18.75" customHeight="1">
-      <c r="B267" s="1"/>
+      <c r="B267" s="26"/>
     </row>
     <row r="268" ht="18.75" customHeight="1">
-      <c r="B268" s="1"/>
+      <c r="B268" s="26"/>
     </row>
     <row r="269" ht="18.75" customHeight="1">
-      <c r="B269" s="1"/>
+      <c r="B269" s="26"/>
     </row>
     <row r="270" ht="18.75" customHeight="1">
-      <c r="B270" s="1"/>
+      <c r="B270" s="26"/>
     </row>
     <row r="271" ht="18.75" customHeight="1">
-      <c r="B271" s="1"/>
+      <c r="B271" s="26"/>
     </row>
     <row r="272" ht="18.75" customHeight="1">
-      <c r="B272" s="1"/>
+      <c r="B272" s="26"/>
     </row>
     <row r="273" ht="18.75" customHeight="1">
-      <c r="B273" s="1"/>
+      <c r="B273" s="26"/>
     </row>
     <row r="274" ht="18.75" customHeight="1">
-      <c r="B274" s="1"/>
+      <c r="B274" s="26"/>
     </row>
     <row r="275" ht="18.75" customHeight="1">
-      <c r="B275" s="1"/>
+      <c r="B275" s="26"/>
     </row>
     <row r="276" ht="18.75" customHeight="1">
-      <c r="B276" s="1"/>
+      <c r="B276" s="26"/>
     </row>
     <row r="277" ht="18.75" customHeight="1">
-      <c r="B277" s="1"/>
+      <c r="B277" s="26"/>
     </row>
     <row r="278" ht="18.75" customHeight="1">
-      <c r="B278" s="1"/>
+      <c r="B278" s="26"/>
     </row>
     <row r="279" ht="18.75" customHeight="1">
-      <c r="B279" s="1"/>
+      <c r="B279" s="26"/>
     </row>
     <row r="280" ht="18.75" customHeight="1">
-      <c r="B280" s="1"/>
+      <c r="B280" s="26"/>
     </row>
     <row r="281" ht="18.75" customHeight="1">
-      <c r="B281" s="1"/>
+      <c r="B281" s="26"/>
     </row>
     <row r="282" ht="18.75" customHeight="1">
-      <c r="B282" s="1"/>
+      <c r="B282" s="26"/>
     </row>
     <row r="283" ht="18.75" customHeight="1">
-      <c r="B283" s="1"/>
+      <c r="B283" s="26"/>
     </row>
     <row r="284" ht="18.75" customHeight="1">
-      <c r="B284" s="1"/>
+      <c r="B284" s="26"/>
     </row>
     <row r="285" ht="18.75" customHeight="1">
-      <c r="B285" s="1"/>
+      <c r="B285" s="26"/>
     </row>
     <row r="286" ht="18.75" customHeight="1">
-      <c r="B286" s="1"/>
+      <c r="B286" s="26"/>
     </row>
     <row r="287" ht="18.75" customHeight="1">
-      <c r="B287" s="1"/>
+      <c r="B287" s="26"/>
     </row>
     <row r="288" ht="18.75" customHeight="1">
-      <c r="B288" s="1"/>
+      <c r="B288" s="26"/>
     </row>
     <row r="289" ht="18.75" customHeight="1">
-      <c r="B289" s="1"/>
+      <c r="B289" s="26"/>
     </row>
     <row r="290" ht="18.75" customHeight="1">
-      <c r="B290" s="1"/>
+      <c r="B290" s="26"/>
     </row>
     <row r="291" ht="18.75" customHeight="1">
-      <c r="B291" s="1"/>
+      <c r="B291" s="26"/>
     </row>
     <row r="292" ht="18.75" customHeight="1">
-      <c r="B292" s="1"/>
+      <c r="B292" s="26"/>
     </row>
     <row r="293" ht="18.75" customHeight="1">
-      <c r="B293" s="1"/>
+      <c r="B293" s="26"/>
     </row>
     <row r="294" ht="18.75" customHeight="1">
-      <c r="B294" s="1"/>
+      <c r="B294" s="26"/>
     </row>
     <row r="295" ht="18.75" customHeight="1">
-      <c r="B295" s="1"/>
+      <c r="B295" s="26"/>
     </row>
     <row r="296" ht="18.75" customHeight="1">
-      <c r="B296" s="1"/>
+      <c r="B296" s="26"/>
     </row>
     <row r="297" ht="18.75" customHeight="1">
-      <c r="B297" s="1"/>
+      <c r="B297" s="26"/>
     </row>
     <row r="298" ht="18.75" customHeight="1">
-      <c r="B298" s="1"/>
+      <c r="B298" s="26"/>
     </row>
     <row r="299" ht="18.75" customHeight="1">
-      <c r="B299" s="1"/>
+      <c r="B299" s="26"/>
     </row>
     <row r="300" ht="18.75" customHeight="1">
-      <c r="B300" s="1"/>
+      <c r="B300" s="26"/>
     </row>
     <row r="301" ht="18.75" customHeight="1">
-      <c r="B301" s="1"/>
+      <c r="B301" s="26"/>
     </row>
     <row r="302" ht="18.75" customHeight="1">
-      <c r="B302" s="1"/>
+      <c r="B302" s="26"/>
     </row>
     <row r="303" ht="18.75" customHeight="1">
-      <c r="B303" s="1"/>
+      <c r="B303" s="26"/>
     </row>
     <row r="304" ht="18.75" customHeight="1">
-      <c r="B304" s="1"/>
+      <c r="B304" s="26"/>
     </row>
     <row r="305" ht="18.75" customHeight="1">
-      <c r="B305" s="1"/>
+      <c r="B305" s="26"/>
     </row>
     <row r="306" ht="18.75" customHeight="1">
-      <c r="B306" s="1"/>
+      <c r="B306" s="26"/>
     </row>
     <row r="307" ht="18.75" customHeight="1">
-      <c r="B307" s="1"/>
+      <c r="B307" s="26"/>
     </row>
     <row r="308" ht="18.75" customHeight="1">
-      <c r="B308" s="1"/>
+      <c r="B308" s="26"/>
     </row>
     <row r="309" ht="18.75" customHeight="1">
-      <c r="B309" s="1"/>
+      <c r="B309" s="26"/>
     </row>
     <row r="310" ht="18.75" customHeight="1">
-      <c r="B310" s="1"/>
+      <c r="B310" s="26"/>
     </row>
     <row r="311" ht="18.75" customHeight="1">
-      <c r="B311" s="1"/>
+      <c r="B311" s="26"/>
     </row>
     <row r="312" ht="18.75" customHeight="1">
-      <c r="B312" s="1"/>
+      <c r="B312" s="26"/>
     </row>
     <row r="313" ht="18.75" customHeight="1">
-      <c r="B313" s="1"/>
+      <c r="B313" s="26"/>
     </row>
     <row r="314" ht="18.75" customHeight="1">
-      <c r="B314" s="1"/>
+      <c r="B314" s="26"/>
     </row>
     <row r="315" ht="18.75" customHeight="1">
-      <c r="B315" s="1"/>
+      <c r="B315" s="26"/>
     </row>
     <row r="316" ht="18.75" customHeight="1">
-      <c r="B316" s="1"/>
+      <c r="B316" s="26"/>
     </row>
     <row r="317" ht="18.75" customHeight="1">
-      <c r="B317" s="1"/>
+      <c r="B317" s="26"/>
     </row>
     <row r="318" ht="18.75" customHeight="1">
-      <c r="B318" s="1"/>
+      <c r="B318" s="26"/>
     </row>
     <row r="319" ht="18.75" customHeight="1">
-      <c r="B319" s="1"/>
+      <c r="B319" s="26"/>
     </row>
     <row r="320" ht="18.75" customHeight="1">
-      <c r="B320" s="1"/>
+      <c r="B320" s="26"/>
     </row>
     <row r="321" ht="18.75" customHeight="1">
-      <c r="B321" s="1"/>
+      <c r="B321" s="26"/>
     </row>
     <row r="322" ht="18.75" customHeight="1">
-      <c r="B322" s="1"/>
+      <c r="B322" s="26"/>
     </row>
     <row r="323" ht="18.75" customHeight="1">
-      <c r="B323" s="1"/>
+      <c r="B323" s="26"/>
     </row>
     <row r="324" ht="18.75" customHeight="1">
-      <c r="B324" s="1"/>
+      <c r="B324" s="26"/>
     </row>
     <row r="325" ht="18.75" customHeight="1">
-      <c r="B325" s="1"/>
+      <c r="B325" s="26"/>
     </row>
     <row r="326" ht="18.75" customHeight="1">
-      <c r="B326" s="1"/>
+      <c r="B326" s="26"/>
     </row>
     <row r="327" ht="18.75" customHeight="1">
-      <c r="B327" s="1"/>
+      <c r="B327" s="26"/>
     </row>
     <row r="328" ht="18.75" customHeight="1">
-      <c r="B328" s="1"/>
+      <c r="B328" s="26"/>
     </row>
     <row r="329" ht="18.75" customHeight="1">
-      <c r="B329" s="1"/>
+      <c r="B329" s="26"/>
     </row>
     <row r="330" ht="18.75" customHeight="1">
-      <c r="B330" s="1"/>
+      <c r="B330" s="26"/>
     </row>
     <row r="331" ht="18.75" customHeight="1">
-      <c r="B331" s="1"/>
+      <c r="B331" s="26"/>
     </row>
     <row r="332" ht="18.75" customHeight="1">
-      <c r="B332" s="1"/>
+      <c r="B332" s="26"/>
     </row>
     <row r="333" ht="18.75" customHeight="1">
-      <c r="B333" s="1"/>
+      <c r="B333" s="26"/>
     </row>
     <row r="334" ht="18.75" customHeight="1">
-      <c r="B334" s="1"/>
+      <c r="B334" s="26"/>
     </row>
     <row r="335" ht="18.75" customHeight="1">
-      <c r="B335" s="1"/>
+      <c r="B335" s="26"/>
     </row>
     <row r="336" ht="18.75" customHeight="1">
-      <c r="B336" s="1"/>
+      <c r="B336" s="26"/>
     </row>
     <row r="337" ht="18.75" customHeight="1">
-      <c r="B337" s="1"/>
+      <c r="B337" s="26"/>
     </row>
     <row r="338" ht="18.75" customHeight="1">
-      <c r="B338" s="1"/>
+      <c r="B338" s="26"/>
     </row>
     <row r="339" ht="18.75" customHeight="1">
-      <c r="B339" s="1"/>
+      <c r="B339" s="26"/>
     </row>
     <row r="340" ht="18.75" customHeight="1">
-      <c r="B340" s="1"/>
+      <c r="B340" s="26"/>
     </row>
     <row r="341" ht="18.75" customHeight="1">
-      <c r="B341" s="1"/>
+      <c r="B341" s="26"/>
     </row>
     <row r="342" ht="18.75" customHeight="1">
-      <c r="B342" s="1"/>
+      <c r="B342" s="26"/>
     </row>
     <row r="343" ht="18.75" customHeight="1">
-      <c r="B343" s="1"/>
+      <c r="B343" s="26"/>
     </row>
     <row r="344" ht="18.75" customHeight="1">
-      <c r="B344" s="1"/>
+      <c r="B344" s="26"/>
     </row>
     <row r="345" ht="18.75" customHeight="1">
-      <c r="B345" s="1"/>
+      <c r="B345" s="26"/>
     </row>
     <row r="346" ht="18.75" customHeight="1">
-      <c r="B346" s="1"/>
+      <c r="B346" s="26"/>
     </row>
     <row r="347" ht="18.75" customHeight="1">
-      <c r="B347" s="1"/>
+      <c r="B347" s="26"/>
     </row>
     <row r="348" ht="18.75" customHeight="1">
-      <c r="B348" s="1"/>
+      <c r="B348" s="26"/>
     </row>
     <row r="349" ht="18.75" customHeight="1">
-      <c r="B349" s="1"/>
+      <c r="B349" s="26"/>
     </row>
     <row r="350" ht="18.75" customHeight="1">
-      <c r="B350" s="1"/>
+      <c r="B350" s="26"/>
     </row>
     <row r="351" ht="18.75" customHeight="1">
-      <c r="B351" s="1"/>
+      <c r="B351" s="26"/>
     </row>
     <row r="352" ht="18.75" customHeight="1">
-      <c r="B352" s="1"/>
+      <c r="B352" s="26"/>
     </row>
     <row r="353" ht="18.75" customHeight="1">
-      <c r="B353" s="1"/>
+      <c r="B353" s="26"/>
     </row>
     <row r="354" ht="18.75" customHeight="1">
-      <c r="B354" s="1"/>
+      <c r="B354" s="26"/>
     </row>
     <row r="355" ht="18.75" customHeight="1">
-      <c r="B355" s="1"/>
+      <c r="B355" s="26"/>
     </row>
     <row r="356" ht="18.75" customHeight="1">
-      <c r="B356" s="1"/>
+      <c r="B356" s="26"/>
     </row>
     <row r="357" ht="18.75" customHeight="1">
-      <c r="B357" s="1"/>
+      <c r="B357" s="26"/>
     </row>
     <row r="358" ht="18.75" customHeight="1">
-      <c r="B358" s="1"/>
+      <c r="B358" s="26"/>
     </row>
     <row r="359" ht="18.75" customHeight="1">
-      <c r="B359" s="1"/>
+      <c r="B359" s="26"/>
     </row>
     <row r="360" ht="18.75" customHeight="1">
-      <c r="B360" s="1"/>
+      <c r="B360" s="26"/>
     </row>
     <row r="361" ht="18.75" customHeight="1">
-      <c r="B361" s="1"/>
+      <c r="B361" s="26"/>
     </row>
     <row r="362" ht="18.75" customHeight="1">
-      <c r="B362" s="1"/>
+      <c r="B362" s="26"/>
     </row>
     <row r="363" ht="18.75" customHeight="1">
-      <c r="B363" s="1"/>
+      <c r="B363" s="26"/>
     </row>
     <row r="364" ht="18.75" customHeight="1">
-      <c r="B364" s="1"/>
+      <c r="B364" s="26"/>
     </row>
     <row r="365" ht="18.75" customHeight="1">
-      <c r="B365" s="1"/>
+      <c r="B365" s="26"/>
     </row>
     <row r="366" ht="18.75" customHeight="1">
-      <c r="B366" s="1"/>
+      <c r="B366" s="26"/>
     </row>
     <row r="367" ht="18.75" customHeight="1">
-      <c r="B367" s="1"/>
+      <c r="B367" s="26"/>
     </row>
     <row r="368" ht="18.75" customHeight="1">
-      <c r="B368" s="1"/>
+      <c r="B368" s="26"/>
     </row>
     <row r="369" ht="18.75" customHeight="1">
-      <c r="B369" s="1"/>
+      <c r="B369" s="26"/>
     </row>
     <row r="370" ht="18.75" customHeight="1">
-      <c r="B370" s="1"/>
+      <c r="B370" s="26"/>
     </row>
     <row r="371" ht="18.75" customHeight="1">
-      <c r="B371" s="1"/>
+      <c r="B371" s="26"/>
     </row>
     <row r="372" ht="18.75" customHeight="1">
-      <c r="B372" s="1"/>
+      <c r="B372" s="26"/>
     </row>
     <row r="373" ht="18.75" customHeight="1">
-      <c r="B373" s="1"/>
+      <c r="B373" s="26"/>
     </row>
     <row r="374" ht="18.75" customHeight="1">
-      <c r="B374" s="1"/>
+      <c r="B374" s="26"/>
     </row>
     <row r="375" ht="18.75" customHeight="1">
-      <c r="B375" s="1"/>
+      <c r="B375" s="26"/>
     </row>
     <row r="376" ht="18.75" customHeight="1">
-      <c r="B376" s="1"/>
+      <c r="B376" s="26"/>
     </row>
     <row r="377" ht="18.75" customHeight="1">
-      <c r="B377" s="1"/>
+      <c r="B377" s="26"/>
     </row>
     <row r="378" ht="18.75" customHeight="1">
-      <c r="B378" s="1"/>
+      <c r="B378" s="26"/>
     </row>
     <row r="379" ht="18.75" customHeight="1">
-      <c r="B379" s="1"/>
+      <c r="B379" s="26"/>
     </row>
     <row r="380" ht="18.75" customHeight="1">
-      <c r="B380" s="1"/>
+      <c r="B380" s="26"/>
     </row>
     <row r="381" ht="18.75" customHeight="1">
-      <c r="B381" s="1"/>
+      <c r="B381" s="26"/>
     </row>
     <row r="382" ht="18.75" customHeight="1">
-      <c r="B382" s="1"/>
+      <c r="B382" s="26"/>
     </row>
     <row r="383" ht="18.75" customHeight="1">
-      <c r="B383" s="1"/>
+      <c r="B383" s="26"/>
     </row>
     <row r="384" ht="18.75" customHeight="1">
-      <c r="B384" s="1"/>
+      <c r="B384" s="26"/>
     </row>
     <row r="385" ht="18.75" customHeight="1">
-      <c r="B385" s="1"/>
+      <c r="B385" s="26"/>
     </row>
     <row r="386" ht="18.75" customHeight="1">
-      <c r="B386" s="1"/>
+      <c r="B386" s="26"/>
     </row>
     <row r="387" ht="18.75" customHeight="1">
-      <c r="B387" s="1"/>
+      <c r="B387" s="26"/>
     </row>
     <row r="388" ht="18.75" customHeight="1">
-      <c r="B388" s="1"/>
+      <c r="B388" s="26"/>
     </row>
     <row r="389" ht="18.75" customHeight="1">
-      <c r="B389" s="1"/>
+      <c r="B389" s="26"/>
     </row>
     <row r="390" ht="18.75" customHeight="1">
-      <c r="B390" s="1"/>
+      <c r="B390" s="26"/>
     </row>
     <row r="391" ht="18.75" customHeight="1">
-      <c r="B391" s="1"/>
+      <c r="B391" s="26"/>
     </row>
     <row r="392" ht="18.75" customHeight="1">
-      <c r="B392" s="1"/>
+      <c r="B392" s="26"/>
     </row>
     <row r="393" ht="18.75" customHeight="1">
-      <c r="B393" s="1"/>
+      <c r="B393" s="26"/>
     </row>
     <row r="394" ht="18.75" customHeight="1">
-      <c r="B394" s="1"/>
+      <c r="B394" s="26"/>
     </row>
     <row r="395" ht="18.75" customHeight="1">
-      <c r="B395" s="1"/>
+      <c r="B395" s="26"/>
     </row>
     <row r="396" ht="18.75" customHeight="1">
-      <c r="B396" s="1"/>
+      <c r="B396" s="26"/>
     </row>
     <row r="397" ht="18.75" customHeight="1">
-      <c r="B397" s="1"/>
+      <c r="B397" s="26"/>
     </row>
     <row r="398" ht="18.75" customHeight="1">
-      <c r="B398" s="1"/>
+      <c r="B398" s="26"/>
     </row>
     <row r="399" ht="18.75" customHeight="1">
-      <c r="B399" s="1"/>
+      <c r="B399" s="26"/>
     </row>
     <row r="400" ht="18.75" customHeight="1">
-      <c r="B400" s="1"/>
+      <c r="B400" s="26"/>
     </row>
     <row r="401" ht="18.75" customHeight="1">
-      <c r="B401" s="1"/>
+      <c r="B401" s="26"/>
     </row>
     <row r="402" ht="18.75" customHeight="1">
-      <c r="B402" s="1"/>
+      <c r="B402" s="26"/>
     </row>
     <row r="403" ht="18.75" customHeight="1">
-      <c r="B403" s="1"/>
+      <c r="B403" s="26"/>
     </row>
     <row r="404" ht="18.75" customHeight="1">
-      <c r="B404" s="1"/>
+      <c r="B404" s="26"/>
     </row>
     <row r="405" ht="18.75" customHeight="1">
-      <c r="B405" s="1"/>
+      <c r="B405" s="26"/>
     </row>
     <row r="406" ht="18.75" customHeight="1">
-      <c r="B406" s="1"/>
+      <c r="B406" s="26"/>
     </row>
     <row r="407" ht="18.75" customHeight="1">
-      <c r="B407" s="1"/>
+      <c r="B407" s="26"/>
     </row>
     <row r="408" ht="18.75" customHeight="1">
-      <c r="B408" s="1"/>
+      <c r="B408" s="26"/>
     </row>
     <row r="409" ht="18.75" customHeight="1">
-      <c r="B409" s="1"/>
+      <c r="B409" s="26"/>
     </row>
     <row r="410" ht="18.75" customHeight="1">
-      <c r="B410" s="1"/>
+      <c r="B410" s="26"/>
     </row>
     <row r="411" ht="18.75" customHeight="1">
-      <c r="B411" s="1"/>
+      <c r="B411" s="26"/>
     </row>
     <row r="412" ht="18.75" customHeight="1">
-      <c r="B412" s="1"/>
+      <c r="B412" s="26"/>
     </row>
     <row r="413" ht="18.75" customHeight="1">
-      <c r="B413" s="1"/>
+      <c r="B413" s="26"/>
     </row>
     <row r="414" ht="18.75" customHeight="1">
-      <c r="B414" s="1"/>
+      <c r="B414" s="26"/>
     </row>
     <row r="415" ht="18.75" customHeight="1">
-      <c r="B415" s="1"/>
+      <c r="B415" s="26"/>
     </row>
     <row r="416" ht="18.75" customHeight="1">
-      <c r="B416" s="1"/>
+      <c r="B416" s="26"/>
     </row>
     <row r="417" ht="18.75" customHeight="1">
-      <c r="B417" s="1"/>
+      <c r="B417" s="26"/>
     </row>
     <row r="418" ht="18.75" customHeight="1">
-      <c r="B418" s="1"/>
+      <c r="B418" s="26"/>
     </row>
     <row r="419" ht="18.75" customHeight="1">
-      <c r="B419" s="1"/>
+      <c r="B419" s="26"/>
     </row>
     <row r="420" ht="18.75" customHeight="1">
-      <c r="B420" s="1"/>
+      <c r="B420" s="26"/>
     </row>
     <row r="421" ht="18.75" customHeight="1">
-      <c r="B421" s="1"/>
+      <c r="B421" s="26"/>
     </row>
     <row r="422" ht="18.75" customHeight="1">
-      <c r="B422" s="1"/>
+      <c r="B422" s="26"/>
     </row>
     <row r="423" ht="18.75" customHeight="1">
-      <c r="B423" s="1"/>
+      <c r="B423" s="26"/>
     </row>
     <row r="424" ht="18.75" customHeight="1">
-      <c r="B424" s="1"/>
+      <c r="B424" s="26"/>
     </row>
     <row r="425" ht="18.75" customHeight="1">
-      <c r="B425" s="1"/>
+      <c r="B425" s="26"/>
     </row>
     <row r="426" ht="18.75" customHeight="1">
-      <c r="B426" s="1"/>
+      <c r="B426" s="26"/>
     </row>
     <row r="427" ht="18.75" customHeight="1">
-      <c r="B427" s="1"/>
+      <c r="B427" s="26"/>
     </row>
     <row r="428" ht="18.75" customHeight="1">
-      <c r="B428" s="1"/>
+      <c r="B428" s="26"/>
     </row>
     <row r="429" ht="18.75" customHeight="1">
-      <c r="B429" s="1"/>
+      <c r="B429" s="26"/>
     </row>
     <row r="430" ht="18.75" customHeight="1">
-      <c r="B430" s="1"/>
+      <c r="B430" s="26"/>
     </row>
     <row r="431" ht="18.75" customHeight="1">
-      <c r="B431" s="1"/>
+      <c r="B431" s="26"/>
     </row>
     <row r="432" ht="18.75" customHeight="1">
-      <c r="B432" s="1"/>
+      <c r="B432" s="26"/>
     </row>
     <row r="433" ht="18.75" customHeight="1">
-      <c r="B433" s="1"/>
+      <c r="B433" s="26"/>
     </row>
     <row r="434" ht="18.75" customHeight="1">
-      <c r="B434" s="1"/>
+      <c r="B434" s="26"/>
     </row>
     <row r="435" ht="18.75" customHeight="1">
-      <c r="B435" s="1"/>
+      <c r="B435" s="26"/>
     </row>
     <row r="436" ht="18.75" customHeight="1">
-      <c r="B436" s="1"/>
+      <c r="B436" s="26"/>
     </row>
     <row r="437" ht="18.75" customHeight="1">
-      <c r="B437" s="1"/>
+      <c r="B437" s="26"/>
     </row>
     <row r="438" ht="18.75" customHeight="1">
-      <c r="B438" s="1"/>
+      <c r="B438" s="26"/>
     </row>
     <row r="439" ht="18.75" customHeight="1">
-      <c r="B439" s="1"/>
+      <c r="B439" s="26"/>
     </row>
     <row r="440" ht="18.75" customHeight="1">
-      <c r="B440" s="1"/>
+      <c r="B440" s="26"/>
     </row>
     <row r="441" ht="18.75" customHeight="1">
-      <c r="B441" s="1"/>
+      <c r="B441" s="26"/>
     </row>
     <row r="442" ht="18.75" customHeight="1">
-      <c r="B442" s="1"/>
+      <c r="B442" s="26"/>
     </row>
     <row r="443" ht="18.75" customHeight="1">
-      <c r="B443" s="1"/>
+      <c r="B443" s="26"/>
     </row>
     <row r="444" ht="18.75" customHeight="1">
-      <c r="B444" s="1"/>
+      <c r="B444" s="26"/>
     </row>
     <row r="445" ht="18.75" customHeight="1">
-      <c r="B445" s="1"/>
+      <c r="B445" s="26"/>
     </row>
     <row r="446" ht="18.75" customHeight="1">
-      <c r="B446" s="1"/>
+      <c r="B446" s="26"/>
     </row>
     <row r="447" ht="18.75" customHeight="1">
-      <c r="B447" s="1"/>
+      <c r="B447" s="26"/>
     </row>
     <row r="448" ht="18.75" customHeight="1">
-      <c r="B448" s="1"/>
+      <c r="B448" s="26"/>
     </row>
     <row r="449" ht="18.75" customHeight="1">
-      <c r="B449" s="1"/>
+      <c r="B449" s="26"/>
     </row>
     <row r="450" ht="18.75" customHeight="1">
-      <c r="B450" s="1"/>
+      <c r="B450" s="26"/>
     </row>
     <row r="451" ht="18.75" customHeight="1">
-      <c r="B451" s="1"/>
+      <c r="B451" s="26"/>
     </row>
     <row r="452" ht="18.75" customHeight="1">
-      <c r="B452" s="1"/>
+      <c r="B452" s="26"/>
     </row>
     <row r="453" ht="18.75" customHeight="1">
-      <c r="B453" s="1"/>
+      <c r="B453" s="26"/>
     </row>
     <row r="454" ht="18.75" customHeight="1">
-      <c r="B454" s="1"/>
+      <c r="B454" s="26"/>
     </row>
     <row r="455" ht="18.75" customHeight="1">
-      <c r="B455" s="1"/>
+      <c r="B455" s="26"/>
     </row>
     <row r="456" ht="18.75" customHeight="1">
-      <c r="B456" s="1"/>
+      <c r="B456" s="26"/>
     </row>
     <row r="457" ht="18.75" customHeight="1">
-      <c r="B457" s="1"/>
+      <c r="B457" s="26"/>
     </row>
     <row r="458" ht="18.75" customHeight="1">
-      <c r="B458" s="1"/>
+      <c r="B458" s="26"/>
     </row>
     <row r="459" ht="18.75" customHeight="1">
-      <c r="B459" s="1"/>
+      <c r="B459" s="26"/>
     </row>
     <row r="460" ht="18.75" customHeight="1">
-      <c r="B460" s="1"/>
+      <c r="B460" s="26"/>
     </row>
     <row r="461" ht="18.75" customHeight="1">
-      <c r="B461" s="1"/>
+      <c r="B461" s="26"/>
     </row>
     <row r="462" ht="18.75" customHeight="1">
-      <c r="B462" s="1"/>
+      <c r="B462" s="26"/>
     </row>
     <row r="463" ht="18.75" customHeight="1">
-      <c r="B463" s="1"/>
+      <c r="B463" s="26"/>
     </row>
     <row r="464" ht="18.75" customHeight="1">
-      <c r="B464" s="1"/>
+      <c r="B464" s="26"/>
     </row>
     <row r="465" ht="18.75" customHeight="1">
-      <c r="B465" s="1"/>
+      <c r="B465" s="26"/>
     </row>
     <row r="466" ht="18.75" customHeight="1">
-      <c r="B466" s="1"/>
+      <c r="B466" s="26"/>
     </row>
     <row r="467" ht="18.75" customHeight="1">
-      <c r="B467" s="1"/>
+      <c r="B467" s="26"/>
     </row>
     <row r="468" ht="18.75" customHeight="1">
-      <c r="B468" s="1"/>
+      <c r="B468" s="26"/>
     </row>
     <row r="469" ht="18.75" customHeight="1">
-      <c r="B469" s="1"/>
+      <c r="B469" s="26"/>
     </row>
     <row r="470" ht="18.75" customHeight="1">
-      <c r="B470" s="1"/>
+      <c r="B470" s="26"/>
     </row>
     <row r="471" ht="18.75" customHeight="1">
-      <c r="B471" s="1"/>
+      <c r="B471" s="26"/>
     </row>
     <row r="472" ht="18.75" customHeight="1">
-      <c r="B472" s="1"/>
+      <c r="B472" s="26"/>
     </row>
     <row r="473" ht="18.75" customHeight="1">
-      <c r="B473" s="1"/>
+      <c r="B473" s="26"/>
     </row>
     <row r="474" ht="18.75" customHeight="1">
-      <c r="B474" s="1"/>
+      <c r="B474" s="26"/>
     </row>
     <row r="475" ht="18.75" customHeight="1">
-      <c r="B475" s="1"/>
+      <c r="B475" s="26"/>
     </row>
     <row r="476" ht="18.75" customHeight="1">
-      <c r="B476" s="1"/>
+      <c r="B476" s="26"/>
     </row>
     <row r="477" ht="18.75" customHeight="1">
-      <c r="B477" s="1"/>
+      <c r="B477" s="26"/>
     </row>
     <row r="478" ht="18.75" customHeight="1">
-      <c r="B478" s="1"/>
+      <c r="B478" s="26"/>
     </row>
     <row r="479" ht="18.75" customHeight="1">
-      <c r="B479" s="1"/>
+      <c r="B479" s="26"/>
     </row>
     <row r="480" ht="18.75" customHeight="1">
-      <c r="B480" s="1"/>
+      <c r="B480" s="26"/>
     </row>
     <row r="481" ht="18.75" customHeight="1">
-      <c r="B481" s="1"/>
+      <c r="B481" s="26"/>
     </row>
     <row r="482" ht="18.75" customHeight="1">
-      <c r="B482" s="1"/>
+      <c r="B482" s="26"/>
     </row>
     <row r="483" ht="18.75" customHeight="1">
-      <c r="B483" s="1"/>
+      <c r="B483" s="26"/>
     </row>
     <row r="484" ht="18.75" customHeight="1">
-      <c r="B484" s="1"/>
+      <c r="B484" s="26"/>
     </row>
     <row r="485" ht="18.75" customHeight="1">
-      <c r="B485" s="1"/>
+      <c r="B485" s="26"/>
     </row>
     <row r="486" ht="18.75" customHeight="1">
-      <c r="B486" s="1"/>
+      <c r="B486" s="26"/>
     </row>
     <row r="487" ht="18.75" customHeight="1">
-      <c r="B487" s="1"/>
+      <c r="B487" s="26"/>
     </row>
     <row r="488" ht="18.75" customHeight="1">
-      <c r="B488" s="1"/>
+      <c r="B488" s="26"/>
     </row>
     <row r="489" ht="18.75" customHeight="1">
-      <c r="B489" s="1"/>
+      <c r="B489" s="26"/>
     </row>
     <row r="490" ht="18.75" customHeight="1">
-      <c r="B490" s="1"/>
+      <c r="B490" s="26"/>
     </row>
     <row r="491" ht="18.75" customHeight="1">
-      <c r="B491" s="1"/>
+      <c r="B491" s="26"/>
     </row>
     <row r="492" ht="18.75" customHeight="1">
-      <c r="B492" s="1"/>
+      <c r="B492" s="26"/>
     </row>
     <row r="493" ht="18.75" customHeight="1">
-      <c r="B493" s="1"/>
+      <c r="B493" s="26"/>
     </row>
     <row r="494" ht="18.75" customHeight="1">
-      <c r="B494" s="1"/>
+      <c r="B494" s="26"/>
     </row>
     <row r="495" ht="18.75" customHeight="1">
-      <c r="B495" s="1"/>
+      <c r="B495" s="26"/>
     </row>
     <row r="496" ht="18.75" customHeight="1">
-      <c r="B496" s="1"/>
+      <c r="B496" s="26"/>
     </row>
     <row r="497" ht="18.75" customHeight="1">
-      <c r="B497" s="1"/>
+      <c r="B497" s="26"/>
     </row>
     <row r="498" ht="18.75" customHeight="1">
-      <c r="B498" s="1"/>
+      <c r="B498" s="26"/>
     </row>
     <row r="499" ht="18.75" customHeight="1">
-      <c r="B499" s="1"/>
+      <c r="B499" s="26"/>
     </row>
     <row r="500" ht="18.75" customHeight="1">
-      <c r="B500" s="1"/>
+      <c r="B500" s="26"/>
     </row>
     <row r="501" ht="18.75" customHeight="1">
-      <c r="B501" s="1"/>
+      <c r="B501" s="26"/>
     </row>
     <row r="502" ht="18.75" customHeight="1">
-      <c r="B502" s="1"/>
+      <c r="B502" s="26"/>
     </row>
     <row r="503" ht="18.75" customHeight="1">
-      <c r="B503" s="1"/>
+      <c r="B503" s="26"/>
     </row>
     <row r="504" ht="18.75" customHeight="1">
-      <c r="B504" s="1"/>
+      <c r="B504" s="26"/>
     </row>
     <row r="505" ht="18.75" customHeight="1">
-      <c r="B505" s="1"/>
+      <c r="B505" s="26"/>
     </row>
     <row r="506" ht="18.75" customHeight="1">
-      <c r="B506" s="1"/>
+      <c r="B506" s="26"/>
     </row>
     <row r="507" ht="18.75" customHeight="1">
-      <c r="B507" s="1"/>
+      <c r="B507" s="26"/>
     </row>
     <row r="508" ht="18.75" customHeight="1">
-      <c r="B508" s="1"/>
+      <c r="B508" s="26"/>
     </row>
     <row r="509" ht="18.75" customHeight="1">
-      <c r="B509" s="1"/>
+      <c r="B509" s="26"/>
     </row>
     <row r="510" ht="18.75" customHeight="1">
-      <c r="B510" s="1"/>
+      <c r="B510" s="26"/>
     </row>
     <row r="511" ht="18.75" customHeight="1">
-      <c r="B511" s="1"/>
+      <c r="B511" s="26"/>
     </row>
     <row r="512" ht="18.75" customHeight="1">
-      <c r="B512" s="1"/>
+      <c r="B512" s="26"/>
     </row>
     <row r="513" ht="18.75" customHeight="1">
-      <c r="B513" s="1"/>
+      <c r="B513" s="26"/>
     </row>
     <row r="514" ht="18.75" customHeight="1">
-      <c r="B514" s="1"/>
+      <c r="B514" s="26"/>
     </row>
     <row r="515" ht="18.75" customHeight="1">
-      <c r="B515" s="1"/>
+      <c r="B515" s="26"/>
     </row>
     <row r="516" ht="18.75" customHeight="1">
-      <c r="B516" s="1"/>
+      <c r="B516" s="26"/>
     </row>
     <row r="517" ht="18.75" customHeight="1">
-      <c r="B517" s="1"/>
+      <c r="B517" s="26"/>
     </row>
     <row r="518" ht="18.75" customHeight="1">
-      <c r="B518" s="1"/>
+      <c r="B518" s="26"/>
     </row>
     <row r="519" ht="18.75" customHeight="1">
-      <c r="B519" s="1"/>
+      <c r="B519" s="26"/>
     </row>
     <row r="520" ht="18.75" customHeight="1">
-      <c r="B520" s="1"/>
+      <c r="B520" s="26"/>
     </row>
     <row r="521" ht="18.75" customHeight="1">
-      <c r="B521" s="1"/>
+      <c r="B521" s="26"/>
     </row>
     <row r="522" ht="18.75" customHeight="1">
-      <c r="B522" s="1"/>
+      <c r="B522" s="26"/>
     </row>
     <row r="523" ht="18.75" customHeight="1">
-      <c r="B523" s="1"/>
+      <c r="B523" s="26"/>
     </row>
     <row r="524" ht="18.75" customHeight="1">
-      <c r="B524" s="1"/>
+      <c r="B524" s="26"/>
     </row>
     <row r="525" ht="18.75" customHeight="1">
-      <c r="B525" s="1"/>
+      <c r="B525" s="26"/>
     </row>
     <row r="526" ht="18.75" customHeight="1">
-      <c r="B526" s="1"/>
+      <c r="B526" s="26"/>
     </row>
     <row r="527" ht="18.75" customHeight="1">
-      <c r="B527" s="1"/>
+      <c r="B527" s="26"/>
     </row>
     <row r="528" ht="18.75" customHeight="1">
-      <c r="B528" s="1"/>
+      <c r="B528" s="26"/>
     </row>
     <row r="529" ht="18.75" customHeight="1">
-      <c r="B529" s="1"/>
+      <c r="B529" s="26"/>
     </row>
     <row r="530" ht="18.75" customHeight="1">
-      <c r="B530" s="1"/>
+      <c r="B530" s="26"/>
     </row>
     <row r="531" ht="18.75" customHeight="1">
-      <c r="B531" s="1"/>
+      <c r="B531" s="26"/>
     </row>
     <row r="532" ht="18.75" customHeight="1">
-      <c r="B532" s="1"/>
+      <c r="B532" s="26"/>
     </row>
     <row r="533" ht="18.75" customHeight="1">
-      <c r="B533" s="1"/>
+      <c r="B533" s="26"/>
     </row>
     <row r="534" ht="18.75" customHeight="1">
-      <c r="B534" s="1"/>
+      <c r="B534" s="26"/>
     </row>
     <row r="535" ht="18.75" customHeight="1">
-      <c r="B535" s="1"/>
+      <c r="B535" s="26"/>
     </row>
     <row r="536" ht="18.75" customHeight="1">
-      <c r="B536" s="1"/>
+      <c r="B536" s="26"/>
     </row>
     <row r="537" ht="18.75" customHeight="1">
-      <c r="B537" s="1"/>
+      <c r="B537" s="26"/>
     </row>
     <row r="538" ht="18.75" customHeight="1">
-      <c r="B538" s="1"/>
+      <c r="B538" s="26"/>
     </row>
     <row r="539" ht="18.75" customHeight="1">
-      <c r="B539" s="1"/>
+      <c r="B539" s="26"/>
     </row>
     <row r="540" ht="18.75" customHeight="1">
-      <c r="B540" s="1"/>
+      <c r="B540" s="26"/>
     </row>
     <row r="541" ht="18.75" customHeight="1">
-      <c r="B541" s="1"/>
+      <c r="B541" s="26"/>
     </row>
     <row r="542" ht="18.75" customHeight="1">
-      <c r="B542" s="1"/>
+      <c r="B542" s="26"/>
     </row>
     <row r="543" ht="18.75" customHeight="1">
-      <c r="B543" s="1"/>
+      <c r="B543" s="26"/>
     </row>
     <row r="544" ht="18.75" customHeight="1">
-      <c r="B544" s="1"/>
+      <c r="B544" s="26"/>
     </row>
     <row r="545" ht="18.75" customHeight="1">
-      <c r="B545" s="1"/>
+      <c r="B545" s="26"/>
     </row>
     <row r="546" ht="18.75" customHeight="1">
-      <c r="B546" s="1"/>
+      <c r="B546" s="26"/>
     </row>
     <row r="547" ht="18.75" customHeight="1">
-      <c r="B547" s="1"/>
+      <c r="B547" s="26"/>
     </row>
     <row r="548" ht="18.75" customHeight="1">
-      <c r="B548" s="1"/>
+      <c r="B548" s="26"/>
     </row>
     <row r="549" ht="18.75" customHeight="1">
-      <c r="B549" s="1"/>
+      <c r="B549" s="26"/>
     </row>
     <row r="550" ht="18.75" customHeight="1">
-      <c r="B550" s="1"/>
+      <c r="B550" s="26"/>
     </row>
     <row r="551" ht="18.75" customHeight="1">
-      <c r="B551" s="1"/>
+      <c r="B551" s="26"/>
     </row>
     <row r="552" ht="18.75" customHeight="1">
-      <c r="B552" s="1"/>
+      <c r="B552" s="26"/>
     </row>
     <row r="553" ht="18.75" customHeight="1">
-      <c r="B553" s="1"/>
+      <c r="B553" s="26"/>
     </row>
     <row r="554" ht="18.75" customHeight="1">
-      <c r="B554" s="1"/>
+      <c r="B554" s="26"/>
     </row>
     <row r="555" ht="18.75" customHeight="1">
-      <c r="B555" s="1"/>
+      <c r="B555" s="26"/>
     </row>
     <row r="556" ht="18.75" customHeight="1">
-      <c r="B556" s="1"/>
+      <c r="B556" s="26"/>
     </row>
     <row r="557" ht="18.75" customHeight="1">
-      <c r="B557" s="1"/>
+      <c r="B557" s="26"/>
     </row>
     <row r="558" ht="18.75" customHeight="1">
-      <c r="B558" s="1"/>
+      <c r="B558" s="26"/>
     </row>
     <row r="559" ht="18.75" customHeight="1">
-      <c r="B559" s="1"/>
+      <c r="B559" s="26"/>
     </row>
     <row r="560" ht="18.75" customHeight="1">
-      <c r="B560" s="1"/>
+      <c r="B560" s="26"/>
     </row>
     <row r="561" ht="18.75" customHeight="1">
-      <c r="B561" s="1"/>
+      <c r="B561" s="26"/>
     </row>
     <row r="562" ht="18.75" customHeight="1">
-      <c r="B562" s="1"/>
+      <c r="B562" s="26"/>
     </row>
     <row r="563" ht="18.75" customHeight="1">
-      <c r="B563" s="1"/>
+      <c r="B563" s="26"/>
     </row>
     <row r="564" ht="18.75" customHeight="1">
-      <c r="B564" s="1"/>
+      <c r="B564" s="26"/>
     </row>
     <row r="565" ht="18.75" customHeight="1">
-      <c r="B565" s="1"/>
+      <c r="B565" s="26"/>
     </row>
     <row r="566" ht="18.75" customHeight="1">
-      <c r="B566" s="1"/>
+      <c r="B566" s="26"/>
     </row>
     <row r="567" ht="18.75" customHeight="1">
-      <c r="B567" s="1"/>
+      <c r="B567" s="26"/>
     </row>
     <row r="568" ht="18.75" customHeight="1">
-      <c r="B568" s="1"/>
+      <c r="B568" s="26"/>
     </row>
     <row r="569" ht="18.75" customHeight="1">
-      <c r="B569" s="1"/>
+      <c r="B569" s="26"/>
     </row>
     <row r="570" ht="18.75" customHeight="1">
-      <c r="B570" s="1"/>
+      <c r="B570" s="26"/>
     </row>
     <row r="571" ht="18.75" customHeight="1">
-      <c r="B571" s="1"/>
+      <c r="B571" s="26"/>
     </row>
     <row r="572" ht="18.75" customHeight="1">
-      <c r="B572" s="1"/>
+      <c r="B572" s="26"/>
     </row>
     <row r="573" ht="18.75" customHeight="1">
-      <c r="B573" s="1"/>
+      <c r="B573" s="26"/>
     </row>
     <row r="574" ht="18.75" customHeight="1">
-      <c r="B574" s="1"/>
+      <c r="B574" s="26"/>
     </row>
     <row r="575" ht="18.75" customHeight="1">
-      <c r="B575" s="1"/>
+      <c r="B575" s="26"/>
     </row>
     <row r="576" ht="18.75" customHeight="1">
-      <c r="B576" s="1"/>
+      <c r="B576" s="26"/>
     </row>
     <row r="577" ht="18.75" customHeight="1">
-      <c r="B577" s="1"/>
+      <c r="B577" s="26"/>
     </row>
     <row r="578" ht="18.75" customHeight="1">
-      <c r="B578" s="1"/>
+      <c r="B578" s="26"/>
     </row>
     <row r="579" ht="18.75" customHeight="1">
-      <c r="B579" s="1"/>
+      <c r="B579" s="26"/>
     </row>
     <row r="580" ht="18.75" customHeight="1">
-      <c r="B580" s="1"/>
+      <c r="B580" s="26"/>
     </row>
     <row r="581" ht="18.75" customHeight="1">
-      <c r="B581" s="1"/>
+      <c r="B581" s="26"/>
     </row>
     <row r="582" ht="18.75" customHeight="1">
-      <c r="B582" s="1"/>
+      <c r="B582" s="26"/>
     </row>
     <row r="583" ht="18.75" customHeight="1">
-      <c r="B583" s="1"/>
+      <c r="B583" s="26"/>
     </row>
     <row r="584" ht="18.75" customHeight="1">
-      <c r="B584" s="1"/>
+      <c r="B584" s="26"/>
     </row>
     <row r="585" ht="18.75" customHeight="1">
-      <c r="B585" s="1"/>
+      <c r="B585" s="26"/>
     </row>
     <row r="586" ht="18.75" customHeight="1">
-      <c r="B586" s="1"/>
+      <c r="B586" s="26"/>
     </row>
     <row r="587" ht="18.75" customHeight="1">
-      <c r="B587" s="1"/>
+      <c r="B587" s="26"/>
     </row>
     <row r="588" ht="18.75" customHeight="1">
-      <c r="B588" s="1"/>
+      <c r="B588" s="26"/>
     </row>
     <row r="589" ht="18.75" customHeight="1">
-      <c r="B589" s="1"/>
+      <c r="B589" s="26"/>
     </row>
     <row r="590" ht="18.75" customHeight="1">
-      <c r="B590" s="1"/>
+      <c r="B590" s="26"/>
     </row>
     <row r="591" ht="18.75" customHeight="1">
-      <c r="B591" s="1"/>
+      <c r="B591" s="26"/>
     </row>
     <row r="592" ht="18.75" customHeight="1">
-      <c r="B592" s="1"/>
+      <c r="B592" s="26"/>
     </row>
     <row r="593" ht="18.75" customHeight="1">
-      <c r="B593" s="1"/>
+      <c r="B593" s="26"/>
     </row>
     <row r="594" ht="18.75" customHeight="1">
-      <c r="B594" s="1"/>
+      <c r="B594" s="26"/>
     </row>
     <row r="595" ht="18.75" customHeight="1">
-      <c r="B595" s="1"/>
+      <c r="B595" s="26"/>
     </row>
     <row r="596" ht="18.75" customHeight="1">
-      <c r="B596" s="1"/>
+      <c r="B596" s="26"/>
     </row>
     <row r="597" ht="18.75" customHeight="1">
-      <c r="B597" s="1"/>
+      <c r="B597" s="26"/>
     </row>
     <row r="598" ht="18.75" customHeight="1">
-      <c r="B598" s="1"/>
+      <c r="B598" s="26"/>
     </row>
     <row r="599" ht="18.75" customHeight="1">
-      <c r="B599" s="1"/>
+      <c r="B599" s="26"/>
     </row>
     <row r="600" ht="18.75" customHeight="1">
-      <c r="B600" s="1"/>
+      <c r="B600" s="26"/>
     </row>
     <row r="601" ht="18.75" customHeight="1">
-      <c r="B601" s="1"/>
+      <c r="B601" s="26"/>
     </row>
     <row r="602" ht="18.75" customHeight="1">
-      <c r="B602" s="1"/>
+      <c r="B602" s="26"/>
     </row>
     <row r="603" ht="18.75" customHeight="1">
-      <c r="B603" s="1"/>
+      <c r="B603" s="26"/>
     </row>
     <row r="604" ht="18.75" customHeight="1">
-      <c r="B604" s="1"/>
+      <c r="B604" s="26"/>
     </row>
     <row r="605" ht="18.75" customHeight="1">
-      <c r="B605" s="1"/>
+      <c r="B605" s="26"/>
     </row>
     <row r="606" ht="18.75" customHeight="1">
-      <c r="B606" s="1"/>
+      <c r="B606" s="26"/>
     </row>
     <row r="607" ht="18.75" customHeight="1">
-      <c r="B607" s="1"/>
+      <c r="B607" s="26"/>
     </row>
     <row r="608" ht="18.75" customHeight="1">
-      <c r="B608" s="1"/>
+      <c r="B608" s="26"/>
     </row>
     <row r="609" ht="18.75" customHeight="1">
-      <c r="B609" s="1"/>
+      <c r="B609" s="26"/>
     </row>
     <row r="610" ht="18.75" customHeight="1">
-      <c r="B610" s="1"/>
+      <c r="B610" s="26"/>
     </row>
     <row r="611" ht="18.75" customHeight="1">
-      <c r="B611" s="1"/>
+      <c r="B611" s="26"/>
     </row>
     <row r="612" ht="18.75" customHeight="1">
-      <c r="B612" s="1"/>
+      <c r="B612" s="26"/>
     </row>
     <row r="613" ht="18.75" customHeight="1">
-      <c r="B613" s="1"/>
+      <c r="B613" s="26"/>
     </row>
     <row r="614" ht="18.75" customHeight="1">
-      <c r="B614" s="1"/>
+      <c r="B614" s="26"/>
     </row>
     <row r="615" ht="18.75" customHeight="1">
-      <c r="B615" s="1"/>
+      <c r="B615" s="26"/>
     </row>
     <row r="616" ht="18.75" customHeight="1">
-      <c r="B616" s="1"/>
+      <c r="B616" s="26"/>
     </row>
     <row r="617" ht="18.75" customHeight="1">
-      <c r="B617" s="1"/>
+      <c r="B617" s="26"/>
     </row>
     <row r="618" ht="18.75" customHeight="1">
-      <c r="B618" s="1"/>
+      <c r="B618" s="26"/>
     </row>
     <row r="619" ht="18.75" customHeight="1">
-      <c r="B619" s="1"/>
+      <c r="B619" s="26"/>
     </row>
     <row r="620" ht="18.75" customHeight="1">
-      <c r="B620" s="1"/>
+      <c r="B620" s="26"/>
     </row>
     <row r="621" ht="18.75" customHeight="1">
-      <c r="B621" s="1"/>
+      <c r="B621" s="26"/>
     </row>
     <row r="622" ht="18.75" customHeight="1">
-      <c r="B622" s="1"/>
+      <c r="B622" s="26"/>
     </row>
     <row r="623" ht="18.75" customHeight="1">
-      <c r="B623" s="1"/>
+      <c r="B623" s="26"/>
     </row>
     <row r="624" ht="18.75" customHeight="1">
-      <c r="B624" s="1"/>
+      <c r="B624" s="26"/>
     </row>
     <row r="625" ht="18.75" customHeight="1">
-      <c r="B625" s="1"/>
+      <c r="B625" s="26"/>
     </row>
     <row r="626" ht="18.75" customHeight="1">
-      <c r="B626" s="1"/>
+      <c r="B626" s="26"/>
     </row>
     <row r="627" ht="18.75" customHeight="1">
-      <c r="B627" s="1"/>
+      <c r="B627" s="26"/>
     </row>
     <row r="628" ht="18.75" customHeight="1">
-      <c r="B628" s="1"/>
+      <c r="B628" s="26"/>
     </row>
     <row r="629" ht="18.75" customHeight="1">
-      <c r="B629" s="1"/>
+      <c r="B629" s="26"/>
     </row>
     <row r="630" ht="18.75" customHeight="1">
-      <c r="B630" s="1"/>
+      <c r="B630" s="26"/>
     </row>
     <row r="631" ht="18.75" customHeight="1">
-      <c r="B631" s="1"/>
+      <c r="B631" s="26"/>
     </row>
     <row r="632" ht="18.75" customHeight="1">
-      <c r="B632" s="1"/>
+      <c r="B632" s="26"/>
     </row>
     <row r="633" ht="18.75" customHeight="1">
-      <c r="B633" s="1"/>
+      <c r="B633" s="26"/>
     </row>
     <row r="634" ht="18.75" customHeight="1">
-      <c r="B634" s="1"/>
+      <c r="B634" s="26"/>
     </row>
     <row r="635" ht="18.75" customHeight="1">
-      <c r="B635" s="1"/>
+      <c r="B635" s="26"/>
     </row>
     <row r="636" ht="18.75" customHeight="1">
-      <c r="B636" s="1"/>
+      <c r="B636" s="26"/>
     </row>
     <row r="637" ht="18.75" customHeight="1">
-      <c r="B637" s="1"/>
+      <c r="B637" s="26"/>
     </row>
     <row r="638" ht="18.75" customHeight="1">
-      <c r="B638" s="1"/>
+      <c r="B638" s="26"/>
     </row>
     <row r="639" ht="18.75" customHeight="1">
-      <c r="B639" s="1"/>
+      <c r="B639" s="26"/>
     </row>
     <row r="640" ht="18.75" customHeight="1">
-      <c r="B640" s="1"/>
+      <c r="B640" s="26"/>
     </row>
     <row r="641" ht="18.75" customHeight="1">
-      <c r="B641" s="1"/>
+      <c r="B641" s="26"/>
     </row>
     <row r="642" ht="18.75" customHeight="1">
-      <c r="B642" s="1"/>
+      <c r="B642" s="26"/>
     </row>
     <row r="643" ht="18.75" customHeight="1">
-      <c r="B643" s="1"/>
+      <c r="B643" s="26"/>
     </row>
     <row r="644" ht="18.75" customHeight="1">
-      <c r="B644" s="1"/>
+      <c r="B644" s="26"/>
     </row>
     <row r="645" ht="18.75" customHeight="1">
-      <c r="B645" s="1"/>
+      <c r="B645" s="26"/>
     </row>
     <row r="646" ht="18.75" customHeight="1">
-      <c r="B646" s="1"/>
+      <c r="B646" s="26"/>
     </row>
     <row r="647" ht="18.75" customHeight="1">
-      <c r="B647" s="1"/>
+      <c r="B647" s="26"/>
     </row>
     <row r="648" ht="18.75" customHeight="1">
-      <c r="B648" s="1"/>
+      <c r="B648" s="26"/>
     </row>
     <row r="649" ht="18.75" customHeight="1">
-      <c r="B649" s="1"/>
+      <c r="B649" s="26"/>
     </row>
     <row r="650" ht="18.75" customHeight="1">
-      <c r="B650" s="1"/>
+      <c r="B650" s="26"/>
     </row>
     <row r="651" ht="18.75" customHeight="1">
-      <c r="B651" s="1"/>
+      <c r="B651" s="26"/>
     </row>
     <row r="652" ht="18.75" customHeight="1">
-      <c r="B652" s="1"/>
+      <c r="B652" s="26"/>
     </row>
     <row r="653" ht="18.75" customHeight="1">
-      <c r="B653" s="1"/>
+      <c r="B653" s="26"/>
     </row>
     <row r="654" ht="18.75" customHeight="1">
-      <c r="B654" s="1"/>
+      <c r="B654" s="26"/>
     </row>
     <row r="655" ht="18.75" customHeight="1">
-      <c r="B655" s="1"/>
+      <c r="B655" s="26"/>
     </row>
     <row r="656" ht="18.75" customHeight="1">
-      <c r="B656" s="1"/>
+      <c r="B656" s="26"/>
     </row>
     <row r="657" ht="18.75" customHeight="1">
-      <c r="B657" s="1"/>
+      <c r="B657" s="26"/>
     </row>
     <row r="658" ht="18.75" customHeight="1">
-      <c r="B658" s="1"/>
+      <c r="B658" s="26"/>
     </row>
     <row r="659" ht="18.75" customHeight="1">
-      <c r="B659" s="1"/>
+      <c r="B659" s="26"/>
     </row>
     <row r="660" ht="18.75" customHeight="1">
-      <c r="B660" s="1"/>
+      <c r="B660" s="26"/>
     </row>
     <row r="661" ht="18.75" customHeight="1">
-      <c r="B661" s="1"/>
+      <c r="B661" s="26"/>
     </row>
     <row r="662" ht="18.75" customHeight="1">
-      <c r="B662" s="1"/>
+      <c r="B662" s="26"/>
     </row>
     <row r="663" ht="18.75" customHeight="1">
-      <c r="B663" s="1"/>
+      <c r="B663" s="26"/>
     </row>
     <row r="664" ht="18.75" customHeight="1">
-      <c r="B664" s="1"/>
+      <c r="B664" s="26"/>
     </row>
     <row r="665" ht="18.75" customHeight="1">
-      <c r="B665" s="1"/>
+      <c r="B665" s="26"/>
     </row>
     <row r="666" ht="18.75" customHeight="1">
-      <c r="B666" s="1"/>
+      <c r="B666" s="26"/>
     </row>
     <row r="667" ht="18.75" customHeight="1">
-      <c r="B667" s="1"/>
+      <c r="B667" s="26"/>
     </row>
     <row r="668" ht="18.75" customHeight="1">
-      <c r="B668" s="1"/>
+      <c r="B668" s="26"/>
     </row>
     <row r="669" ht="18.75" customHeight="1">
-      <c r="B669" s="1"/>
+      <c r="B669" s="26"/>
     </row>
     <row r="670" ht="18.75" customHeight="1">
-      <c r="B670" s="1"/>
+      <c r="B670" s="26"/>
     </row>
     <row r="671" ht="18.75" customHeight="1">
-      <c r="B671" s="1"/>
+      <c r="B671" s="26"/>
     </row>
     <row r="672" ht="18.75" customHeight="1">
-      <c r="B672" s="1"/>
+      <c r="B672" s="26"/>
     </row>
     <row r="673" ht="18.75" customHeight="1">
-      <c r="B673" s="1"/>
+      <c r="B673" s="26"/>
     </row>
     <row r="674" ht="18.75" customHeight="1">
-      <c r="B674" s="1"/>
+      <c r="B674" s="26"/>
     </row>
     <row r="675" ht="18.75" customHeight="1">
-      <c r="B675" s="1"/>
+      <c r="B675" s="26"/>
     </row>
     <row r="676" ht="18.75" customHeight="1">
-      <c r="B676" s="1"/>
+      <c r="B676" s="26"/>
     </row>
     <row r="677" ht="18.75" customHeight="1">
-      <c r="B677" s="1"/>
+      <c r="B677" s="26"/>
     </row>
     <row r="678" ht="18.75" customHeight="1">
-      <c r="B678" s="1"/>
+      <c r="B678" s="26"/>
     </row>
     <row r="679" ht="18.75" customHeight="1">
-      <c r="B679" s="1"/>
+      <c r="B679" s="26"/>
     </row>
     <row r="680" ht="18.75" customHeight="1">
-      <c r="B680" s="1"/>
+      <c r="B680" s="26"/>
     </row>
     <row r="681" ht="18.75" customHeight="1">
-      <c r="B681" s="1"/>
+      <c r="B681" s="26"/>
     </row>
     <row r="682" ht="18.75" customHeight="1">
-      <c r="B682" s="1"/>
+      <c r="B682" s="26"/>
     </row>
     <row r="683" ht="18.75" customHeight="1">
-      <c r="B683" s="1"/>
+      <c r="B683" s="26"/>
     </row>
     <row r="684" ht="18.75" customHeight="1">
-      <c r="B684" s="1"/>
+      <c r="B684" s="26"/>
     </row>
     <row r="685" ht="18.75" customHeight="1">
-      <c r="B685" s="1"/>
+      <c r="B685" s="26"/>
     </row>
     <row r="686" ht="18.75" customHeight="1">
-      <c r="B686" s="1"/>
+      <c r="B686" s="26"/>
     </row>
     <row r="687" ht="18.75" customHeight="1">
-      <c r="B687" s="1"/>
+      <c r="B687" s="26"/>
     </row>
     <row r="688" ht="18.75" customHeight="1">
-      <c r="B688" s="1"/>
+      <c r="B688" s="26"/>
     </row>
     <row r="689" ht="18.75" customHeight="1">
-      <c r="B689" s="1"/>
+      <c r="B689" s="26"/>
     </row>
     <row r="690" ht="18.75" customHeight="1">
-      <c r="B690" s="1"/>
+      <c r="B690" s="26"/>
     </row>
     <row r="691" ht="18.75" customHeight="1">
-      <c r="B691" s="1"/>
+      <c r="B691" s="26"/>
     </row>
     <row r="692" ht="18.75" customHeight="1">
-      <c r="B692" s="1"/>
+      <c r="B692" s="26"/>
     </row>
     <row r="693" ht="18.75" customHeight="1">
-      <c r="B693" s="1"/>
+      <c r="B693" s="26"/>
     </row>
     <row r="694" ht="18.75" customHeight="1">
-      <c r="B694" s="1"/>
+      <c r="B694" s="26"/>
     </row>
     <row r="695" ht="18.75" customHeight="1">
-      <c r="B695" s="1"/>
+      <c r="B695" s="26"/>
     </row>
     <row r="696" ht="18.75" customHeight="1">
-      <c r="B696" s="1"/>
+      <c r="B696" s="26"/>
     </row>
     <row r="697" ht="18.75" customHeight="1">
-      <c r="B697" s="1"/>
+      <c r="B697" s="26"/>
     </row>
     <row r="698" ht="18.75" customHeight="1">
-      <c r="B698" s="1"/>
+      <c r="B698" s="26"/>
     </row>
     <row r="699" ht="18.75" customHeight="1">
-      <c r="B699" s="1"/>
+      <c r="B699" s="26"/>
     </row>
     <row r="700" ht="18.75" customHeight="1">
-      <c r="B700" s="1"/>
+      <c r="B700" s="26"/>
     </row>
     <row r="701" ht="18.75" customHeight="1">
-      <c r="B701" s="1"/>
+      <c r="B701" s="26"/>
     </row>
     <row r="702" ht="18.75" customHeight="1">
-      <c r="B702" s="1"/>
+      <c r="B702" s="26"/>
     </row>
     <row r="703" ht="18.75" customHeight="1">
-      <c r="B703" s="1"/>
+      <c r="B703" s="26"/>
     </row>
     <row r="704" ht="18.75" customHeight="1">
-      <c r="B704" s="1"/>
+      <c r="B704" s="26"/>
     </row>
     <row r="705" ht="18.75" customHeight="1">
-      <c r="B705" s="1"/>
+      <c r="B705" s="26"/>
     </row>
     <row r="706" ht="18.75" customHeight="1">
-      <c r="B706" s="1"/>
+      <c r="B706" s="26"/>
     </row>
     <row r="707" ht="18.75" customHeight="1">
-      <c r="B707" s="1"/>
+      <c r="B707" s="26"/>
     </row>
     <row r="708" ht="18.75" customHeight="1">
-      <c r="B708" s="1"/>
+      <c r="B708" s="26"/>
     </row>
     <row r="709" ht="18.75" customHeight="1">
-      <c r="B709" s="1"/>
+      <c r="B709" s="26"/>
     </row>
     <row r="710" ht="18.75" customHeight="1">
-      <c r="B710" s="1"/>
+      <c r="B710" s="26"/>
     </row>
     <row r="711" ht="18.75" customHeight="1">
-      <c r="B711" s="1"/>
+      <c r="B711" s="26"/>
     </row>
     <row r="712" ht="18.75" customHeight="1">
-      <c r="B712" s="1"/>
+      <c r="B712" s="26"/>
     </row>
     <row r="713" ht="18.75" customHeight="1">
-      <c r="B713" s="1"/>
+      <c r="B713" s="26"/>
     </row>
     <row r="714" ht="18.75" customHeight="1">
-      <c r="B714" s="1"/>
+      <c r="B714" s="26"/>
     </row>
     <row r="715" ht="18.75" customHeight="1">
-      <c r="B715" s="1"/>
+      <c r="B715" s="26"/>
     </row>
     <row r="716" ht="18.75" customHeight="1">
-      <c r="B716" s="1"/>
+      <c r="B716" s="26"/>
     </row>
     <row r="717" ht="18.75" customHeight="1">
-      <c r="B717" s="1"/>
+      <c r="B717" s="26"/>
     </row>
     <row r="718" ht="18.75" customHeight="1">
-      <c r="B718" s="1"/>
+      <c r="B718" s="26"/>
     </row>
     <row r="719" ht="18.75" customHeight="1">
-      <c r="B719" s="1"/>
+      <c r="B719" s="26"/>
     </row>
     <row r="720" ht="18.75" customHeight="1">
-      <c r="B720" s="1"/>
+      <c r="B720" s="26"/>
     </row>
     <row r="721" ht="18.75" customHeight="1">
-      <c r="B721" s="1"/>
+      <c r="B721" s="26"/>
     </row>
     <row r="722" ht="18.75" customHeight="1">
-      <c r="B722" s="1"/>
+      <c r="B722" s="26"/>
     </row>
     <row r="723" ht="18.75" customHeight="1">
-      <c r="B723" s="1"/>
+      <c r="B723" s="26"/>
     </row>
     <row r="724" ht="18.75" customHeight="1">
-      <c r="B724" s="1"/>
+      <c r="B724" s="26"/>
     </row>
     <row r="725" ht="18.75" customHeight="1">
-      <c r="B725" s="1"/>
+      <c r="B725" s="26"/>
     </row>
     <row r="726" ht="18.75" customHeight="1">
-      <c r="B726" s="1"/>
+      <c r="B726" s="26"/>
     </row>
     <row r="727" ht="18.75" customHeight="1">
-      <c r="B727" s="1"/>
+      <c r="B727" s="26"/>
     </row>
     <row r="728" ht="18.75" customHeight="1">
-      <c r="B728" s="1"/>
+      <c r="B728" s="26"/>
     </row>
     <row r="729" ht="18.75" customHeight="1">
-      <c r="B729" s="1"/>
+      <c r="B729" s="26"/>
     </row>
     <row r="730" ht="18.75" customHeight="1">
-      <c r="B730" s="1"/>
+      <c r="B730" s="26"/>
     </row>
     <row r="731" ht="18.75" customHeight="1">
-      <c r="B731" s="1"/>
+      <c r="B731" s="26"/>
     </row>
     <row r="732" ht="18.75" customHeight="1">
-      <c r="B732" s="1"/>
+      <c r="B732" s="26"/>
     </row>
     <row r="733" ht="18.75" customHeight="1">
-      <c r="B733" s="1"/>
+      <c r="B733" s="26"/>
     </row>
     <row r="734" ht="18.75" customHeight="1">
-      <c r="B734" s="1"/>
+      <c r="B734" s="26"/>
     </row>
     <row r="735" ht="18.75" customHeight="1">
-      <c r="B735" s="1"/>
+      <c r="B735" s="26"/>
     </row>
     <row r="736" ht="18.75" customHeight="1">
-      <c r="B736" s="1"/>
+      <c r="B736" s="26"/>
     </row>
     <row r="737" ht="18.75" customHeight="1">
-      <c r="B737" s="1"/>
+      <c r="B737" s="26"/>
     </row>
     <row r="738" ht="18.75" customHeight="1">
-      <c r="B738" s="1"/>
+      <c r="B738" s="26"/>
     </row>
     <row r="739" ht="18.75" customHeight="1">
-      <c r="B739" s="1"/>
+      <c r="B739" s="26"/>
     </row>
     <row r="740" ht="18.75" customHeight="1">
-      <c r="B740" s="1"/>
+      <c r="B740" s="26"/>
     </row>
     <row r="741" ht="18.75" customHeight="1">
-      <c r="B741" s="1"/>
+      <c r="B741" s="26"/>
     </row>
     <row r="742" ht="18.75" customHeight="1">
-      <c r="B742" s="1"/>
+      <c r="B742" s="26"/>
     </row>
     <row r="743" ht="18.75" customHeight="1">
-      <c r="B743" s="1"/>
+      <c r="B743" s="26"/>
     </row>
     <row r="744" ht="18.75" customHeight="1">
-      <c r="B744" s="1"/>
+      <c r="B744" s="26"/>
     </row>
     <row r="745" ht="18.75" customHeight="1">
-      <c r="B745" s="1"/>
+      <c r="B745" s="26"/>
     </row>
     <row r="746" ht="18.75" customHeight="1">
-      <c r="B746" s="1"/>
+      <c r="B746" s="26"/>
     </row>
     <row r="747" ht="18.75" customHeight="1">
-      <c r="B747" s="1"/>
+      <c r="B747" s="26"/>
     </row>
     <row r="748" ht="18.75" customHeight="1">
-      <c r="B748" s="1"/>
+      <c r="B748" s="26"/>
     </row>
     <row r="749" ht="18.75" customHeight="1">
-      <c r="B749" s="1"/>
+      <c r="B749" s="26"/>
     </row>
     <row r="750" ht="18.75" customHeight="1">
-      <c r="B750" s="1"/>
+      <c r="B750" s="26"/>
     </row>
     <row r="751" ht="18.75" customHeight="1">
-      <c r="B751" s="1"/>
+      <c r="B751" s="26"/>
     </row>
     <row r="752" ht="18.75" customHeight="1">
-      <c r="B752" s="1"/>
+      <c r="B752" s="26"/>
     </row>
     <row r="753" ht="18.75" customHeight="1">
-      <c r="B753" s="1"/>
+      <c r="B753" s="26"/>
     </row>
     <row r="754" ht="18.75" customHeight="1">
-      <c r="B754" s="1"/>
+      <c r="B754" s="26"/>
     </row>
     <row r="755" ht="18.75" customHeight="1">
-      <c r="B755" s="1"/>
+      <c r="B755" s="26"/>
     </row>
     <row r="756" ht="18.75" customHeight="1">
-      <c r="B756" s="1"/>
+      <c r="B756" s="26"/>
     </row>
     <row r="757" ht="18.75" customHeight="1">
-      <c r="B757" s="1"/>
+      <c r="B757" s="26"/>
     </row>
     <row r="758" ht="18.75" customHeight="1">
-      <c r="B758" s="1"/>
+      <c r="B758" s="26"/>
     </row>
     <row r="759" ht="18.75" customHeight="1">
-      <c r="B759" s="1"/>
+      <c r="B759" s="26"/>
     </row>
     <row r="760" ht="18.75" customHeight="1">
-      <c r="B760" s="1"/>
+      <c r="B760" s="26"/>
     </row>
     <row r="761" ht="18.75" customHeight="1">
-      <c r="B761" s="1"/>
+      <c r="B761" s="26"/>
     </row>
     <row r="762" ht="18.75" customHeight="1">
-      <c r="B762" s="1"/>
+      <c r="B762" s="26"/>
     </row>
     <row r="763" ht="18.75" customHeight="1">
-      <c r="B763" s="1"/>
+      <c r="B763" s="26"/>
     </row>
     <row r="764" ht="18.75" customHeight="1">
-      <c r="B764" s="1"/>
+      <c r="B764" s="26"/>
     </row>
     <row r="765" ht="18.75" customHeight="1">
-      <c r="B765" s="1"/>
+      <c r="B765" s="26"/>
     </row>
     <row r="766" ht="18.75" customHeight="1">
-      <c r="B766" s="1"/>
+      <c r="B766" s="26"/>
     </row>
     <row r="767" ht="18.75" customHeight="1">
-      <c r="B767" s="1"/>
+      <c r="B767" s="26"/>
     </row>
     <row r="768" ht="18.75" customHeight="1">
-      <c r="B768" s="1"/>
+      <c r="B768" s="26"/>
     </row>
     <row r="769" ht="18.75" customHeight="1">
-      <c r="B769" s="1"/>
+      <c r="B769" s="26"/>
     </row>
     <row r="770" ht="18.75" customHeight="1">
-      <c r="B770" s="1"/>
+      <c r="B770" s="26"/>
     </row>
     <row r="771" ht="18.75" customHeight="1">
-      <c r="B771" s="1"/>
+      <c r="B771" s="26"/>
     </row>
     <row r="772" ht="18.75" customHeight="1">
-      <c r="B772" s="1"/>
+      <c r="B772" s="26"/>
     </row>
     <row r="773" ht="18.75" customHeight="1">
-      <c r="B773" s="1"/>
+      <c r="B773" s="26"/>
     </row>
     <row r="774" ht="18.75" customHeight="1">
-      <c r="B774" s="1"/>
+      <c r="B774" s="26"/>
     </row>
     <row r="775" ht="18.75" customHeight="1">
-      <c r="B775" s="1"/>
+      <c r="B775" s="26"/>
     </row>
     <row r="776" ht="18.75" customHeight="1">
-      <c r="B776" s="1"/>
+      <c r="B776" s="26"/>
     </row>
     <row r="777" ht="18.75" customHeight="1">
-      <c r="B777" s="1"/>
+      <c r="B777" s="26"/>
     </row>
     <row r="778" ht="18.75" customHeight="1">
-      <c r="B778" s="1"/>
+      <c r="B778" s="26"/>
     </row>
     <row r="779" ht="18.75" customHeight="1">
-      <c r="B779" s="1"/>
+      <c r="B779" s="26"/>
     </row>
     <row r="780" ht="18.75" customHeight="1">
-      <c r="B780" s="1"/>
+      <c r="B780" s="26"/>
     </row>
     <row r="781" ht="18.75" customHeight="1">
-      <c r="B781" s="1"/>
+      <c r="B781" s="26"/>
     </row>
     <row r="782" ht="18.75" customHeight="1">
-      <c r="B782" s="1"/>
+      <c r="B782" s="26"/>
     </row>
     <row r="783" ht="18.75" customHeight="1">
-      <c r="B783" s="1"/>
+      <c r="B783" s="26"/>
     </row>
     <row r="784" ht="18.75" customHeight="1">
-      <c r="B784" s="1"/>
+      <c r="B784" s="26"/>
     </row>
     <row r="785" ht="18.75" customHeight="1">
-      <c r="B785" s="1"/>
+      <c r="B785" s="26"/>
     </row>
     <row r="786" ht="18.75" customHeight="1">
-      <c r="B786" s="1"/>
+      <c r="B786" s="26"/>
     </row>
     <row r="787" ht="18.75" customHeight="1">
-      <c r="B787" s="1"/>
+      <c r="B787" s="26"/>
     </row>
     <row r="788" ht="18.75" customHeight="1">
-      <c r="B788" s="1"/>
+      <c r="B788" s="26"/>
     </row>
     <row r="789" ht="18.75" customHeight="1">
-      <c r="B789" s="1"/>
+      <c r="B789" s="26"/>
     </row>
     <row r="790" ht="18.75" customHeight="1">
-      <c r="B790" s="1"/>
+      <c r="B790" s="26"/>
     </row>
     <row r="791" ht="18.75" customHeight="1">
-      <c r="B791" s="1"/>
+      <c r="B791" s="26"/>
     </row>
     <row r="792" ht="18.75" customHeight="1">
-      <c r="B792" s="1"/>
+      <c r="B792" s="26"/>
     </row>
     <row r="793" ht="18.75" customHeight="1">
-      <c r="B793" s="1"/>
+      <c r="B793" s="26"/>
     </row>
     <row r="794" ht="18.75" customHeight="1">
-      <c r="B794" s="1"/>
+      <c r="B794" s="26"/>
     </row>
     <row r="795" ht="18.75" customHeight="1">
-      <c r="B795" s="1"/>
+      <c r="B795" s="26"/>
     </row>
     <row r="796" ht="18.75" customHeight="1">
-      <c r="B796" s="1"/>
+      <c r="B796" s="26"/>
     </row>
     <row r="797" ht="18.75" customHeight="1">
-      <c r="B797" s="1"/>
+      <c r="B797" s="26"/>
     </row>
     <row r="798" ht="18.75" customHeight="1">
-      <c r="B798" s="1"/>
+      <c r="B798" s="26"/>
     </row>
     <row r="799" ht="18.75" customHeight="1">
-      <c r="B799" s="1"/>
+      <c r="B799" s="26"/>
     </row>
     <row r="800" ht="18.75" customHeight="1">
-      <c r="B800" s="1"/>
+      <c r="B800" s="26"/>
     </row>
     <row r="801" ht="18.75" customHeight="1">
-      <c r="B801" s="1"/>
+      <c r="B801" s="26"/>
     </row>
     <row r="802" ht="18.75" customHeight="1">
-      <c r="B802" s="1"/>
+      <c r="B802" s="26"/>
     </row>
     <row r="803" ht="18.75" customHeight="1">
-      <c r="B803" s="1"/>
+      <c r="B803" s="26"/>
     </row>
     <row r="804" ht="18.75" customHeight="1">
-      <c r="B804" s="1"/>
+      <c r="B804" s="26"/>
     </row>
     <row r="805" ht="18.75" customHeight="1">
-      <c r="B805" s="1"/>
+      <c r="B805" s="26"/>
     </row>
     <row r="806" ht="18.75" customHeight="1">
-      <c r="B806" s="1"/>
+      <c r="B806" s="26"/>
     </row>
     <row r="807" ht="18.75" customHeight="1">
-      <c r="B807" s="1"/>
+      <c r="B807" s="26"/>
     </row>
     <row r="808" ht="18.75" customHeight="1">
-      <c r="B808" s="1"/>
+      <c r="B808" s="26"/>
     </row>
     <row r="809" ht="18.75" customHeight="1">
-      <c r="B809" s="1"/>
+      <c r="B809" s="26"/>
     </row>
     <row r="810" ht="18.75" customHeight="1">
-      <c r="B810" s="1"/>
+      <c r="B810" s="26"/>
     </row>
     <row r="811" ht="18.75" customHeight="1">
-      <c r="B811" s="1"/>
+      <c r="B811" s="26"/>
     </row>
     <row r="812" ht="18.75" customHeight="1">
-      <c r="B812" s="1"/>
+      <c r="B812" s="26"/>
     </row>
     <row r="813" ht="18.75" customHeight="1">
-      <c r="B813" s="1"/>
+      <c r="B813" s="26"/>
     </row>
     <row r="814" ht="18.75" customHeight="1">
-      <c r="B814" s="1"/>
+      <c r="B814" s="26"/>
     </row>
     <row r="815" ht="18.75" customHeight="1">
-      <c r="B815" s="1"/>
+      <c r="B815" s="26"/>
     </row>
     <row r="816" ht="18.75" customHeight="1">
-      <c r="B816" s="1"/>
+      <c r="B816" s="26"/>
     </row>
     <row r="817" ht="18.75" customHeight="1">
-      <c r="B817" s="1"/>
+      <c r="B817" s="26"/>
     </row>
     <row r="818" ht="18.75" customHeight="1">
-      <c r="B818" s="1"/>
+      <c r="B818" s="26"/>
     </row>
     <row r="819" ht="18.75" customHeight="1">
-      <c r="B819" s="1"/>
+      <c r="B819" s="26"/>
     </row>
     <row r="820" ht="18.75" customHeight="1">
-      <c r="B820" s="1"/>
+      <c r="B820" s="26"/>
     </row>
     <row r="821" ht="18.75" customHeight="1">
-      <c r="B821" s="1"/>
+      <c r="B821" s="26"/>
     </row>
     <row r="822" ht="18.75" customHeight="1">
-      <c r="B822" s="1"/>
+      <c r="B822" s="26"/>
     </row>
     <row r="823" ht="18.75" customHeight="1">
-      <c r="B823" s="1"/>
+      <c r="B823" s="26"/>
     </row>
     <row r="824" ht="18.75" customHeight="1">
-      <c r="B824" s="1"/>
+      <c r="B824" s="26"/>
     </row>
     <row r="825" ht="18.75" customHeight="1">
-      <c r="B825" s="1"/>
+      <c r="B825" s="26"/>
     </row>
     <row r="826" ht="18.75" customHeight="1">
-      <c r="B826" s="1"/>
+      <c r="B826" s="26"/>
     </row>
     <row r="827" ht="18.75" customHeight="1">
-      <c r="B827" s="1"/>
+      <c r="B827" s="26"/>
     </row>
     <row r="828" ht="18.75" customHeight="1">
-      <c r="B828" s="1"/>
+      <c r="B828" s="26"/>
     </row>
     <row r="829" ht="18.75" customHeight="1">
-      <c r="B829" s="1"/>
+      <c r="B829" s="26"/>
     </row>
     <row r="830" ht="18.75" customHeight="1">
-      <c r="B830" s="1"/>
+      <c r="B830" s="26"/>
     </row>
     <row r="831" ht="18.75" customHeight="1">
-      <c r="B831" s="1"/>
+      <c r="B831" s="26"/>
     </row>
     <row r="832" ht="18.75" customHeight="1">
-      <c r="B832" s="1"/>
+      <c r="B832" s="26"/>
     </row>
     <row r="833" ht="18.75" customHeight="1">
-      <c r="B833" s="1"/>
+      <c r="B833" s="26"/>
     </row>
     <row r="834" ht="18.75" customHeight="1">
-      <c r="B834" s="1"/>
+      <c r="B834" s="26"/>
     </row>
     <row r="835" ht="18.75" customHeight="1">
-      <c r="B835" s="1"/>
+      <c r="B835" s="26"/>
     </row>
     <row r="836" ht="18.75" customHeight="1">
-      <c r="B836" s="1"/>
+      <c r="B836" s="26"/>
     </row>
     <row r="837" ht="18.75" customHeight="1">
-      <c r="B837" s="1"/>
+      <c r="B837" s="26"/>
     </row>
     <row r="838" ht="18.75" customHeight="1">
-      <c r="B838" s="1"/>
+      <c r="B838" s="26"/>
     </row>
     <row r="839" ht="18.75" customHeight="1">
-      <c r="B839" s="1"/>
+      <c r="B839" s="26"/>
     </row>
     <row r="840" ht="18.75" customHeight="1">
-      <c r="B840" s="1"/>
+      <c r="B840" s="26"/>
     </row>
     <row r="841" ht="18.75" customHeight="1">
-      <c r="B841" s="1"/>
+      <c r="B841" s="26"/>
     </row>
     <row r="842" ht="18.75" customHeight="1">
-      <c r="B842" s="1"/>
+      <c r="B842" s="26"/>
     </row>
     <row r="843" ht="18.75" customHeight="1">
-      <c r="B843" s="1"/>
+      <c r="B843" s="26"/>
     </row>
     <row r="844" ht="18.75" customHeight="1">
-      <c r="B844" s="1"/>
+      <c r="B844" s="26"/>
     </row>
     <row r="845" ht="18.75" customHeight="1">
-      <c r="B845" s="1"/>
+      <c r="B845" s="26"/>
     </row>
     <row r="846" ht="18.75" customHeight="1">
-      <c r="B846" s="1"/>
+      <c r="B846" s="26"/>
     </row>
     <row r="847" ht="18.75" customHeight="1">
-      <c r="B847" s="1"/>
+      <c r="B847" s="26"/>
     </row>
     <row r="848" ht="18.75" customHeight="1">
-      <c r="B848" s="1"/>
+      <c r="B848" s="26"/>
     </row>
     <row r="849" ht="18.75" customHeight="1">
-      <c r="B849" s="1"/>
+      <c r="B849" s="26"/>
     </row>
     <row r="850" ht="18.75" customHeight="1">
-      <c r="B850" s="1"/>
+      <c r="B850" s="26"/>
     </row>
     <row r="851" ht="18.75" customHeight="1">
-      <c r="B851" s="1"/>
+      <c r="B851" s="26"/>
     </row>
     <row r="852" ht="18.75" customHeight="1">
-      <c r="B852" s="1"/>
+      <c r="B852" s="26"/>
     </row>
     <row r="853" ht="18.75" customHeight="1">
-      <c r="B853" s="1"/>
+      <c r="B853" s="26"/>
     </row>
     <row r="854" ht="18.75" customHeight="1">
-      <c r="B854" s="1"/>
+      <c r="B854" s="26"/>
     </row>
     <row r="855" ht="18.75" customHeight="1">
-      <c r="B855" s="1"/>
+      <c r="B855" s="26"/>
     </row>
     <row r="856" ht="18.75" customHeight="1">
-      <c r="B856" s="1"/>
+      <c r="B856" s="26"/>
     </row>
     <row r="857" ht="18.75" customHeight="1">
-      <c r="B857" s="1"/>
+      <c r="B857" s="26"/>
     </row>
     <row r="858" ht="18.75" customHeight="1">
-      <c r="B858" s="1"/>
+      <c r="B858" s="26"/>
     </row>
     <row r="859" ht="18.75" customHeight="1">
-      <c r="B859" s="1"/>
+      <c r="B859" s="26"/>
     </row>
     <row r="860" ht="18.75" customHeight="1">
-      <c r="B860" s="1"/>
+      <c r="B860" s="26"/>
     </row>
     <row r="861" ht="18.75" customHeight="1">
-      <c r="B861" s="1"/>
+      <c r="B861" s="26"/>
     </row>
     <row r="862" ht="18.75" customHeight="1">
-      <c r="B862" s="1"/>
+      <c r="B862" s="26"/>
     </row>
     <row r="863" ht="18.75" customHeight="1">
-      <c r="B863" s="1"/>
+      <c r="B863" s="26"/>
     </row>
     <row r="864" ht="18.75" customHeight="1">
-      <c r="B864" s="1"/>
+      <c r="B864" s="26"/>
     </row>
     <row r="865" ht="18.75" customHeight="1">
-      <c r="B865" s="1"/>
+      <c r="B865" s="26"/>
     </row>
     <row r="866" ht="18.75" customHeight="1">
-      <c r="B866" s="1"/>
+      <c r="B866" s="26"/>
     </row>
     <row r="867" ht="18.75" customHeight="1">
-      <c r="B867" s="1"/>
+      <c r="B867" s="26"/>
     </row>
     <row r="868" ht="18.75" customHeight="1">
-      <c r="B868" s="1"/>
+      <c r="B868" s="26"/>
     </row>
     <row r="869" ht="18.75" customHeight="1">
-      <c r="B869" s="1"/>
+      <c r="B869" s="26"/>
     </row>
     <row r="870" ht="18.75" customHeight="1">
-      <c r="B870" s="1"/>
+      <c r="B870" s="26"/>
     </row>
     <row r="871" ht="18.75" customHeight="1">
-      <c r="B871" s="1"/>
+      <c r="B871" s="26"/>
     </row>
     <row r="872" ht="18.75" customHeight="1">
-      <c r="B872" s="1"/>
+      <c r="B872" s="26"/>
     </row>
     <row r="873" ht="18.75" customHeight="1">
-      <c r="B873" s="1"/>
+      <c r="B873" s="26"/>
     </row>
     <row r="874" ht="18.75" customHeight="1">
-      <c r="B874" s="1"/>
+      <c r="B874" s="26"/>
     </row>
     <row r="875" ht="18.75" customHeight="1">
-      <c r="B875" s="1"/>
+      <c r="B875" s="26"/>
     </row>
     <row r="876" ht="18.75" customHeight="1">
-      <c r="B876" s="1"/>
+      <c r="B876" s="26"/>
     </row>
     <row r="877" ht="18.75" customHeight="1">
-      <c r="B877" s="1"/>
+      <c r="B877" s="26"/>
     </row>
     <row r="878" ht="18.75" customHeight="1">
-      <c r="B878" s="1"/>
+      <c r="B878" s="26"/>
     </row>
     <row r="879" ht="18.75" customHeight="1">
-      <c r="B879" s="1"/>
+      <c r="B879" s="26"/>
     </row>
     <row r="880" ht="18.75" customHeight="1">
-      <c r="B880" s="1"/>
+      <c r="B880" s="26"/>
     </row>
     <row r="881" ht="18.75" customHeight="1">
-      <c r="B881" s="1"/>
+      <c r="B881" s="26"/>
     </row>
     <row r="882" ht="18.75" customHeight="1">
-      <c r="B882" s="1"/>
+      <c r="B882" s="26"/>
     </row>
     <row r="883" ht="18.75" customHeight="1">
-      <c r="B883" s="1"/>
+      <c r="B883" s="26"/>
     </row>
     <row r="884" ht="18.75" customHeight="1">
-      <c r="B884" s="1"/>
+      <c r="B884" s="26"/>
     </row>
     <row r="885" ht="18.75" customHeight="1">
-      <c r="B885" s="1"/>
+      <c r="B885" s="26"/>
     </row>
     <row r="886" ht="18.75" customHeight="1">
-      <c r="B886" s="1"/>
+      <c r="B886" s="26"/>
     </row>
     <row r="887" ht="18.75" customHeight="1">
-      <c r="B887" s="1"/>
+      <c r="B887" s="26"/>
     </row>
     <row r="888" ht="18.75" customHeight="1">
-      <c r="B888" s="1"/>
+      <c r="B888" s="26"/>
     </row>
     <row r="889" ht="18.75" customHeight="1">
-      <c r="B889" s="1"/>
+      <c r="B889" s="26"/>
     </row>
     <row r="890" ht="18.75" customHeight="1">
-      <c r="B890" s="1"/>
+      <c r="B890" s="26"/>
     </row>
     <row r="891" ht="18.75" customHeight="1">
-      <c r="B891" s="1"/>
+      <c r="B891" s="26"/>
     </row>
     <row r="892" ht="18.75" customHeight="1">
-      <c r="B892" s="1"/>
+      <c r="B892" s="26"/>
     </row>
     <row r="893" ht="18.75" customHeight="1">
-      <c r="B893" s="1"/>
+      <c r="B893" s="26"/>
     </row>
     <row r="894" ht="18.75" customHeight="1">
-      <c r="B894" s="1"/>
+      <c r="B894" s="26"/>
     </row>
     <row r="895" ht="18.75" customHeight="1">
-      <c r="B895" s="1"/>
+      <c r="B895" s="26"/>
     </row>
     <row r="896" ht="18.75" customHeight="1">
-      <c r="B896" s="1"/>
+      <c r="B896" s="26"/>
     </row>
     <row r="897" ht="18.75" customHeight="1">
-      <c r="B897" s="1"/>
+      <c r="B897" s="26"/>
     </row>
     <row r="898" ht="18.75" customHeight="1">
-      <c r="B898" s="1"/>
+      <c r="B898" s="26"/>
     </row>
     <row r="899" ht="18.75" customHeight="1">
-      <c r="B899" s="1"/>
+      <c r="B899" s="26"/>
     </row>
     <row r="900" ht="18.75" customHeight="1">
-      <c r="B900" s="1"/>
+      <c r="B900" s="26"/>
     </row>
     <row r="901" ht="18.75" customHeight="1">
-      <c r="B901" s="1"/>
+      <c r="B901" s="26"/>
     </row>
     <row r="902" ht="18.75" customHeight="1">
-      <c r="B902" s="1"/>
+      <c r="B902" s="26"/>
     </row>
     <row r="903" ht="18.75" customHeight="1">
-      <c r="B903" s="1"/>
+      <c r="B903" s="26"/>
     </row>
     <row r="904" ht="18.75" customHeight="1">
-      <c r="B904" s="1"/>
+      <c r="B904" s="26"/>
     </row>
     <row r="905" ht="18.75" customHeight="1">
-      <c r="B905" s="1"/>
+      <c r="B905" s="26"/>
     </row>
     <row r="906" ht="18.75" customHeight="1">
-      <c r="B906" s="1"/>
+      <c r="B906" s="26"/>
     </row>
     <row r="907" ht="18.75" customHeight="1">
-      <c r="B907" s="1"/>
+      <c r="B907" s="26"/>
     </row>
     <row r="908" ht="18.75" customHeight="1">
-      <c r="B908" s="1"/>
+      <c r="B908" s="26"/>
     </row>
     <row r="909" ht="18.75" customHeight="1">
-      <c r="B909" s="1"/>
+      <c r="B909" s="26"/>
     </row>
     <row r="910" ht="18.75" customHeight="1">
-      <c r="B910" s="1"/>
+      <c r="B910" s="26"/>
     </row>
     <row r="911" ht="18.75" customHeight="1">
-      <c r="B911" s="1"/>
+      <c r="B911" s="26"/>
     </row>
     <row r="912" ht="18.75" customHeight="1">
-      <c r="B912" s="1"/>
+      <c r="B912" s="26"/>
     </row>
     <row r="913" ht="18.75" customHeight="1">
-      <c r="B913" s="1"/>
+      <c r="B913" s="26"/>
     </row>
     <row r="914" ht="18.75" customHeight="1">
-      <c r="B914" s="1"/>
+      <c r="B914" s="26"/>
     </row>
     <row r="915" ht="18.75" customHeight="1">
-      <c r="B915" s="1"/>
+      <c r="B915" s="26"/>
     </row>
     <row r="916" ht="18.75" customHeight="1">
-      <c r="B916" s="1"/>
+      <c r="B916" s="26"/>
     </row>
     <row r="917" ht="18.75" customHeight="1">
-      <c r="B917" s="1"/>
+      <c r="B917" s="26"/>
     </row>
     <row r="918" ht="18.75" customHeight="1">
-      <c r="B918" s="1"/>
+      <c r="B918" s="26"/>
     </row>
     <row r="919" ht="18.75" customHeight="1">
-      <c r="B919" s="1"/>
+      <c r="B919" s="26"/>
     </row>
     <row r="920" ht="18.75" customHeight="1">
-      <c r="B920" s="1"/>
+      <c r="B920" s="26"/>
     </row>
     <row r="921" ht="18.75" customHeight="1">
-      <c r="B921" s="1"/>
+      <c r="B921" s="26"/>
     </row>
     <row r="922" ht="18.75" customHeight="1">
-      <c r="B922" s="1"/>
+      <c r="B922" s="26"/>
     </row>
     <row r="923" ht="18.75" customHeight="1">
-      <c r="B923" s="1"/>
+      <c r="B923" s="26"/>
     </row>
     <row r="924" ht="18.75" customHeight="1">
-      <c r="B924" s="1"/>
+      <c r="B924" s="26"/>
     </row>
     <row r="925" ht="18.75" customHeight="1">
-      <c r="B925" s="1"/>
+      <c r="B925" s="26"/>
     </row>
     <row r="926" ht="18.75" customHeight="1">
-      <c r="B926" s="1"/>
+      <c r="B926" s="26"/>
     </row>
     <row r="927" ht="18.75" customHeight="1">
-      <c r="B927" s="1"/>
+      <c r="B927" s="26"/>
     </row>
     <row r="928" ht="18.75" customHeight="1">
-      <c r="B928" s="1"/>
+      <c r="B928" s="26"/>
     </row>
     <row r="929" ht="18.75" customHeight="1">
-      <c r="B929" s="1"/>
+      <c r="B929" s="26"/>
     </row>
     <row r="930" ht="18.75" customHeight="1">
-      <c r="B930" s="1"/>
+      <c r="B930" s="26"/>
     </row>
     <row r="931" ht="18.75" customHeight="1">
-      <c r="B931" s="1"/>
+      <c r="B931" s="26"/>
     </row>
     <row r="932" ht="18.75" customHeight="1">
-      <c r="B932" s="1"/>
+      <c r="B932" s="26"/>
     </row>
     <row r="933" ht="18.75" customHeight="1">
-      <c r="B933" s="1"/>
+      <c r="B933" s="26"/>
     </row>
     <row r="934" ht="18.75" customHeight="1">
-      <c r="B934" s="1"/>
+      <c r="B934" s="26"/>
     </row>
     <row r="935" ht="18.75" customHeight="1">
-      <c r="B935" s="1"/>
+      <c r="B935" s="26"/>
     </row>
     <row r="936" ht="18.75" customHeight="1">
-      <c r="B936" s="1"/>
+      <c r="B936" s="26"/>
     </row>
     <row r="937" ht="18.75" customHeight="1">
-      <c r="B937" s="1"/>
+      <c r="B937" s="26"/>
     </row>
     <row r="938" ht="18.75" customHeight="1">
-      <c r="B938" s="1"/>
+      <c r="B938" s="26"/>
     </row>
     <row r="939" ht="18.75" customHeight="1">
-      <c r="B939" s="1"/>
+      <c r="B939" s="26"/>
     </row>
     <row r="940" ht="18.75" customHeight="1">
-      <c r="B940" s="1"/>
+      <c r="B940" s="26"/>
     </row>
     <row r="941" ht="18.75" customHeight="1">
-      <c r="B941" s="1"/>
+      <c r="B941" s="26"/>
     </row>
     <row r="942" ht="18.75" customHeight="1">
-      <c r="B942" s="1"/>
+      <c r="B942" s="26"/>
     </row>
     <row r="943" ht="18.75" customHeight="1">
-      <c r="B943" s="1"/>
+      <c r="B943" s="26"/>
     </row>
     <row r="944" ht="18.75" customHeight="1">
-      <c r="B944" s="1"/>
+      <c r="B944" s="26"/>
     </row>
     <row r="945" ht="18.75" customHeight="1">
-      <c r="B945" s="1"/>
+      <c r="B945" s="26"/>
     </row>
     <row r="946" ht="18.75" customHeight="1">
-      <c r="B946" s="1"/>
+      <c r="B946" s="26"/>
     </row>
     <row r="947" ht="18.75" customHeight="1">
-      <c r="B947" s="1"/>
+      <c r="B947" s="26"/>
     </row>
     <row r="948" ht="18.75" customHeight="1">
-      <c r="B948" s="1"/>
+      <c r="B948" s="26"/>
     </row>
     <row r="949" ht="18.75" customHeight="1">
-      <c r="B949" s="1"/>
+      <c r="B949" s="26"/>
     </row>
     <row r="950" ht="18.75" customHeight="1">
-      <c r="B950" s="1"/>
+      <c r="B950" s="26"/>
     </row>
     <row r="951" ht="18.75" customHeight="1">
-      <c r="B951" s="1"/>
+      <c r="B951" s="26"/>
     </row>
     <row r="952" ht="18.75" customHeight="1">
-      <c r="B952" s="1"/>
+      <c r="B952" s="26"/>
     </row>
     <row r="953" ht="18.75" customHeight="1">
-      <c r="B953" s="1"/>
+      <c r="B953" s="26"/>
     </row>
     <row r="954" ht="18.75" customHeight="1">
-      <c r="B954" s="1"/>
+      <c r="B954" s="26"/>
     </row>
     <row r="955" ht="18.75" customHeight="1">
-      <c r="B955" s="1"/>
+      <c r="B955" s="26"/>
     </row>
     <row r="956" ht="18.75" customHeight="1">
-      <c r="B956" s="1"/>
+      <c r="B956" s="26"/>
     </row>
     <row r="957" ht="18.75" customHeight="1">
-      <c r="B957" s="1"/>
+      <c r="B957" s="26"/>
     </row>
     <row r="958" ht="18.75" customHeight="1">
-      <c r="B958" s="1"/>
+      <c r="B958" s="26"/>
     </row>
     <row r="959" ht="18.75" customHeight="1">
-      <c r="B959" s="1"/>
+      <c r="B959" s="26"/>
     </row>
     <row r="960" ht="18.75" customHeight="1">
-      <c r="B960" s="1"/>
+      <c r="B960" s="26"/>
     </row>
     <row r="961" ht="18.75" customHeight="1">
-      <c r="B961" s="1"/>
+      <c r="B961" s="26"/>
     </row>
     <row r="962" ht="18.75" customHeight="1">
-      <c r="B962" s="1"/>
+      <c r="B962" s="26"/>
     </row>
     <row r="963" ht="18.75" customHeight="1">
-      <c r="B963" s="1"/>
+      <c r="B963" s="26"/>
     </row>
     <row r="964" ht="18.75" customHeight="1">
-      <c r="B964" s="1"/>
+      <c r="B964" s="26"/>
     </row>
     <row r="965" ht="18.75" customHeight="1">
-      <c r="B965" s="1"/>
+      <c r="B965" s="26"/>
     </row>
     <row r="966" ht="18.75" customHeight="1">
-      <c r="B966" s="1"/>
+      <c r="B966" s="26"/>
     </row>
     <row r="967" ht="18.75" customHeight="1">
-      <c r="B967" s="1"/>
+      <c r="B967" s="26"/>
     </row>
     <row r="968" ht="18.75" customHeight="1">
-      <c r="B968" s="1"/>
+      <c r="B968" s="26"/>
     </row>
     <row r="969" ht="18.75" customHeight="1">
-      <c r="B969" s="1"/>
+      <c r="B969" s="26"/>
     </row>
     <row r="970" ht="18.75" customHeight="1">
-      <c r="B970" s="1"/>
+      <c r="B970" s="26"/>
     </row>
     <row r="971" ht="18.75" customHeight="1">
-      <c r="B971" s="1"/>
+      <c r="B971" s="26"/>
     </row>
     <row r="972" ht="18.75" customHeight="1">
-      <c r="B972" s="1"/>
+      <c r="B972" s="26"/>
     </row>
     <row r="973" ht="18.75" customHeight="1">
-      <c r="B973" s="1"/>
+      <c r="B973" s="26"/>
     </row>
     <row r="974" ht="18.75" customHeight="1">
-      <c r="B974" s="1"/>
+      <c r="B974" s="26"/>
     </row>
     <row r="975" ht="18.75" customHeight="1">
-      <c r="B975" s="1"/>
+      <c r="B975" s="26"/>
     </row>
     <row r="976" ht="18.75" customHeight="1">
-      <c r="B976" s="1"/>
+      <c r="B976" s="26"/>
     </row>
     <row r="977" ht="18.75" customHeight="1">
-      <c r="B977" s="1"/>
+      <c r="B977" s="26"/>
     </row>
     <row r="978" ht="18.75" customHeight="1">
-      <c r="B978" s="1"/>
+      <c r="B978" s="26"/>
     </row>
     <row r="979" ht="18.75" customHeight="1">
-      <c r="B979" s="1"/>
+      <c r="B979" s="26"/>
     </row>
     <row r="980" ht="18.75" customHeight="1">
-      <c r="B980" s="1"/>
+      <c r="B980" s="26"/>
     </row>
     <row r="981" ht="18.75" customHeight="1">
-      <c r="B981" s="1"/>
+      <c r="B981" s="26"/>
     </row>
     <row r="982" ht="18.75" customHeight="1">
-      <c r="B982" s="1"/>
+      <c r="B982" s="26"/>
     </row>
     <row r="983" ht="18.75" customHeight="1">
-      <c r="B983" s="1"/>
+      <c r="B983" s="26"/>
     </row>
     <row r="984" ht="18.75" customHeight="1">
-      <c r="B984" s="1"/>
+      <c r="B984" s="26"/>
     </row>
     <row r="985" ht="18.75" customHeight="1">
-      <c r="B985" s="1"/>
+      <c r="B985" s="26"/>
     </row>
     <row r="986" ht="18.75" customHeight="1">
-      <c r="B986" s="1"/>
+      <c r="B986" s="26"/>
     </row>
     <row r="987" ht="18.75" customHeight="1">
-      <c r="B987" s="1"/>
+      <c r="B987" s="26"/>
     </row>
     <row r="988" ht="18.75" customHeight="1">
-      <c r="B988" s="1"/>
+      <c r="B988" s="26"/>
     </row>
     <row r="989" ht="18.75" customHeight="1">
-      <c r="B989" s="1"/>
+      <c r="B989" s="26"/>
     </row>
     <row r="990" ht="18.75" customHeight="1">
-      <c r="B990" s="1"/>
+      <c r="B990" s="26"/>
     </row>
     <row r="991" ht="18.75" customHeight="1">
-      <c r="B991" s="1"/>
+      <c r="B991" s="26"/>
     </row>
     <row r="992" ht="18.75" customHeight="1">
-      <c r="B992" s="1"/>
+      <c r="B992" s="26"/>
     </row>
     <row r="993" ht="18.75" customHeight="1">
-      <c r="B993" s="1"/>
+      <c r="B993" s="26"/>
     </row>
     <row r="994" ht="18.75" customHeight="1">
-      <c r="B994" s="1"/>
+      <c r="B994" s="26"/>
     </row>
     <row r="995" ht="18.75" customHeight="1">
-      <c r="B995" s="1"/>
+      <c r="B995" s="26"/>
     </row>
     <row r="996" ht="18.75" customHeight="1">
-      <c r="B996" s="1"/>
+      <c r="B996" s="26"/>
     </row>
     <row r="997" ht="18.75" customHeight="1">
-      <c r="B997" s="1"/>
+      <c r="B997" s="26"/>
     </row>
     <row r="998" ht="18.75" customHeight="1">
-      <c r="B998" s="1"/>
+      <c r="B998" s="26"/>
     </row>
     <row r="999" ht="18.75" customHeight="1">
-      <c r="B999" s="1"/>
+      <c r="B999" s="26"/>
     </row>
     <row r="1000" ht="18.75" customHeight="1">
-      <c r="B1000" s="1"/>
+      <c r="B1000" s="26"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/src/main/resources/client-labels/ami-etiquetas-template.xlsx
+++ b/src/main/resources/client-labels/ami-etiquetas-template.xlsx
@@ -8,17 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jordi\Documents\Workspace\Packing List Automation\docs\Etiquetas cajas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE2F7A4-F485-4C89-BE47-6410CB2DE7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BF3FA6-0560-44FB-82D5-09F339FA9DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AMI CHINA" sheetId="1" r:id="rId1"/>
     <sheet name="AMI JAPAN" sheetId="2" r:id="rId2"/>
     <sheet name="AMI FRANCE" sheetId="3" r:id="rId3"/>
+    <sheet name="Etiquetas Palets JAPAN" sheetId="9" r:id="rId4"/>
+    <sheet name="Etiquetas Palets CHINA" sheetId="10" r:id="rId5"/>
+    <sheet name="Etiquetas Palets FRANCE" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'AMI FRANCE'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Etiquetas Palets CHINA'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Etiquetas Palets FRANCE'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Etiquetas Palets JAPAN'!$A$1:$D$15</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="55">
   <si>
     <t>DHL GLOBAL FORWARDING CO.LTD</t>
   </si>
@@ -294,6 +300,131 @@
   <si>
     <t>14 / 84</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DESTINATAIRE
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Consignee)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nombre total de colis sur la palette
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Total number of packages on the palette)</t>
+    </r>
+  </si>
+  <si>
+    <t>64,58 Kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C/O AMI	
+N°305 HUTING RD	
+SONG JIANG DISTRICT	
+201616 SHANGHAI
+CHINA	</t>
+  </si>
+  <si>
+    <t>Nº 1 à Nº 12</t>
+  </si>
+  <si>
+    <t>FRANCE</t>
+  </si>
+  <si>
+    <t>AMI PARIS JAPAN
+MARUNI BUSINESS
+LOGISTICS CORPORATION - IBL PLAZA
+5-13, Chidori-Cho, Ichikawa-Shi
+272-0126 CHIBA - JAPAN</t>
+  </si>
+  <si>
+    <t>PUNTOTRES BAGS &amp; BELTS, S.L. C/INDUSTRIA 585-587 
+08918 BADALONA 
+SPAIN</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DESTINATION
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Destination)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EXPEDITEUR
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Shipper / Sender)
+PROVENANCE
+(Origin)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Poids brut 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Total gross weight)</t>
+    </r>
+  </si>
+  <si>
+    <t>A.PARIS
+21 avenue Saint Mathurins
+60000 ALLONNE
+FRANCE</t>
+  </si>
+  <si>
+    <t>Nº 12 à Nº 24</t>
+  </si>
 </sst>
 </file>
 
@@ -302,11 +433,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -472,8 +610,58 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,8 +686,14 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -809,207 +1003,262 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{1CA08267-AE73-40A6-8026-149D4D03D50B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1946,34 +2195,34 @@
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="64"/>
+      <c r="C2" s="58"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62"/>
+      <c r="C3" s="60"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="62"/>
+      <c r="C4" s="60"/>
     </row>
     <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="62"/>
+      <c r="C5" s="60"/>
     </row>
     <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="62"/>
+      <c r="C6" s="60"/>
     </row>
     <row r="7" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1991,19 +2240,19 @@
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="63">
         <v>7703</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="6"/>
-      <c r="C10" s="60"/>
+      <c r="C10" s="64"/>
     </row>
     <row r="11" spans="2:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="61" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2011,7 +2260,7 @@
       <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="62"/>
     </row>
     <row r="13" spans="2:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
@@ -2055,34 +2304,34 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="58"/>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="62"/>
+      <c r="C20" s="60"/>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="60"/>
     </row>
     <row r="22" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="62"/>
+      <c r="C22" s="60"/>
     </row>
     <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="60"/>
     </row>
     <row r="24" spans="2:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
@@ -2100,19 +2349,19 @@
       <c r="B26" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="59">
+      <c r="C26" s="63">
         <v>7703</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="6"/>
-      <c r="C27" s="60"/>
+      <c r="C27" s="64"/>
     </row>
     <row r="28" spans="2:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="61" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2120,7 +2369,7 @@
       <c r="B29" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="58"/>
+      <c r="C29" s="62"/>
     </row>
     <row r="30" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
@@ -3130,11 +3379,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="C26:C27"/>
@@ -3144,6 +3388,11 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
@@ -3164,26 +3413,26 @@
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="64"/>
+      <c r="C2" s="58"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
     </row>
     <row r="4" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="62"/>
+      <c r="C4" s="60"/>
     </row>
     <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="62"/>
+      <c r="C5" s="60"/>
     </row>
     <row r="6" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
@@ -3201,13 +3450,13 @@
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="63">
         <v>7697</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
-      <c r="C9" s="60"/>
+      <c r="C9" s="64"/>
     </row>
     <row r="10" spans="2:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
@@ -3268,26 +3517,26 @@
       <c r="B17" s="36"/>
     </row>
     <row r="18" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="58"/>
     </row>
     <row r="19" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="61"/>
-      <c r="C19" s="62"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
     </row>
     <row r="20" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="62"/>
+      <c r="C20" s="60"/>
     </row>
     <row r="21" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="60"/>
     </row>
     <row r="22" spans="2:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
@@ -3305,13 +3554,13 @@
       <c r="B24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="63">
         <v>7697</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="6"/>
-      <c r="C25" s="60"/>
+      <c r="C25" s="64"/>
     </row>
     <row r="26" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
@@ -4337,11 +4586,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="C8:C9"/>
@@ -4349,6 +4593,11 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.15748031496062992" bottom="0.15748031496062992" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -7528,4 +7777,343 @@
   <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B601899D-4438-4E83-A234-FFA0F93CF2B1}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="B1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" style="71" customWidth="1"/>
+    <col min="2" max="2" width="38.21875" style="71" customWidth="1"/>
+    <col min="3" max="3" width="44.21875" style="71" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="71" customWidth="1"/>
+    <col min="5" max="16384" width="11.5546875" style="71"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="81.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="76"/>
+    </row>
+    <row r="6" spans="2:5" ht="75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="2:5" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="81.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="80" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="76"/>
+    </row>
+    <row r="13" spans="2:5" ht="75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9128A729-64F1-48A2-8EAC-F3A5FD408861}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="B1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" style="71" customWidth="1"/>
+    <col min="2" max="2" width="38.21875" style="71" customWidth="1"/>
+    <col min="3" max="3" width="44.21875" style="71" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="71" customWidth="1"/>
+    <col min="5" max="16384" width="11.5546875" style="71"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="81.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="80" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="76"/>
+    </row>
+    <row r="6" spans="2:5" ht="75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="2:5" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="81.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="80" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="76"/>
+    </row>
+    <row r="13" spans="2:5" ht="75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C782E10-FDCF-4A17-B641-599E54C5B36C}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="B1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" style="71" customWidth="1"/>
+    <col min="2" max="2" width="38.21875" style="71" customWidth="1"/>
+    <col min="3" max="3" width="44.21875" style="71" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="71" customWidth="1"/>
+    <col min="5" max="16384" width="11.5546875" style="71"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="81.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="72" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="76"/>
+    </row>
+    <row r="6" spans="2:5" ht="75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="2:5" ht="88.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="81.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="79" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="76"/>
+    </row>
+    <row r="13" spans="2:5" ht="75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>